--- a/reports/rxkids_2028/rxkids_2028_cost_and_impact.xlsx
+++ b/reports/rxkids_2028/rxkids_2028_cost_and_impact.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -591,55 +591,85 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>HOUSEHOLD REACH</t>
+          <t>POTENTIAL — extend postnatal 6→12 months (optional)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>Families reached (weighted)</t>
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Additional cost (+6 months)</t>
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>306411</v>
+        <v>16148563.2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
+          <t xml:space="preserve">  Total cost (12-month design)</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>68693606.40000001</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>HOUSEHOLD REACH</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Families reached (weighted)</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>306411</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
           <t xml:space="preserve">  Prenatal (expectant filers)</t>
         </is>
       </c>
-      <c r="B16" s="5" t="n">
+      <c r="B20" s="5" t="n">
         <v>245248</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">  Postnatal (families w/ infants)</t>
         </is>
       </c>
-      <c r="B17" s="5" t="n">
+      <c r="B21" s="5" t="n">
         <v>96130</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>Avg benefit per family reached</t>
         </is>
       </c>
-      <c r="B18" s="5" t="n">
+      <c r="B22" s="5" t="n">
         <v>171.4854988887475</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>Benefits by income quintile → see the 'By income quintile' tab.</t>
         </is>
@@ -1213,7 +1243,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1262,7 +1292,7 @@
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t>Caveats: 2026-2028 FPL is CPI-projected off the 2025 HHS table; pregnancy incidence and infant share are held at base-year values.</t>
+          <t>The base run prices the 6-month postnatal window (Flint's lower bound). The 'potential' line prices the optional extension to the full 12 months — the program may or may not opt in. Postnatal cost is linear in months, so the additional 6 months roughly equals the base postnatal arm again.</t>
         </is>
       </c>
     </row>
@@ -1271,6 +1301,16 @@
     </row>
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>Caveats: 2026-2028 FPL is CPI-projected off the 2025 HHS table; pregnancy incidence and infant share are held at base-year values.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>Full methodology: RXKIDS_METHODOLOGY.md (program origin, parameter sourcing, eligibility approximations, limitations).</t>
         </is>

--- a/reports/rxkids_2028/rxkids_2028_cost_and_impact.xlsx
+++ b/reports/rxkids_2028/rxkids_2028_cost_and_impact.xlsx
@@ -23,7 +23,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -39,6 +39,11 @@
     <font>
       <i val="1"/>
       <color rgb="00555555"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <i val="1"/>
+      <color rgb="00B00000"/>
     </font>
     <font>
       <b val="1"/>
@@ -92,15 +97,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -477,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -498,178 +505,275 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>⚠ Point estimate — true uncertainty is ±30-40%. RxKids has no admin caseload to calibrate against; cost hinges on soft pregnancy/infant incidence assumptions. Read with the assumption band below.</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>FISCAL COST (annual)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Total program cost</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n">
-        <v>52545043.2</v>
+      <c r="B5" s="6" t="n">
+        <v>48445689.59999999</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Prenatal arm</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n">
-        <v>36396480</v>
+      <c r="B6" s="6" t="n">
+        <v>16148563.2</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Postnatal arm</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n">
-        <v>16148563.2</v>
+      <c r="B7" s="6" t="n">
+        <v>32297126.4</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>Sampling 90% CI — low</t>
         </is>
       </c>
-      <c r="B8" s="5" t="n">
-        <v>50318825.275288</v>
+      <c r="B8" s="6" t="n">
+        <v>45627472.49774296</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>Sampling 90% CI — high</t>
         </is>
       </c>
-      <c r="B9" s="5" t="n">
-        <v>54771261.12471201</v>
+      <c r="B9" s="6" t="n">
+        <v>51263906.70225703</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  SDR standard error</t>
         </is>
       </c>
-      <c r="B10" s="5" t="n">
-        <v>1353323.966390275</v>
+      <c r="B10" s="6" t="n">
+        <v>1713201.885870538</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>Assumption band — low</t>
         </is>
       </c>
-      <c r="B11" s="5" t="n">
-        <v>39408782.4</v>
+      <c r="B11" s="6" t="n">
+        <v>27250700.4</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>Assumption band — high</t>
         </is>
       </c>
-      <c r="B12" s="5" t="n">
-        <v>62397238.8</v>
+      <c r="B12" s="6" t="n">
+        <v>71911570.5</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr"/>
+      <c r="A13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>POTENTIAL — extend postnatal 6→12 months (optional)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Additional cost (+6 months)</t>
         </is>
       </c>
-      <c r="B15" s="5" t="n">
-        <v>16148563.2</v>
+      <c r="B15" s="6" t="n">
+        <v>32297126.40000001</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Total cost (12-month design)</t>
         </is>
       </c>
-      <c r="B16" s="5" t="n">
-        <v>68693606.40000001</v>
+      <c r="B16" s="6" t="n">
+        <v>80742816</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr"/>
+      <c r="A17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>FIRST FISCAL YEAR (launch) — 12mo operating, 12mo ramp</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Year-1 disbursement (total)</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>20260465.86666667</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Prenatal</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>8747138.4</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Postnatal</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n">
+        <v>11513327.46666667</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    (postnatal deferred to next FY)</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n">
+        <v>5980949.333333332</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Year-1 as % of steady state</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="n">
+        <v>41.8</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Year-1 if ramp = 6mo (fast)</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n">
+        <v>31624269.6</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Year-1 if ramp = 18mo (slow)</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n">
+        <v>13506977.24444444</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>HOUSEHOLD REACH</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>Families reached (weighted)</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="n">
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Eligible families (weighted)</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n">
         <v>306411</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Prenatal (expectant filers)</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="n">
-        <v>245248</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Postnatal (families w/ infants)</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="n">
-        <v>96130</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>Avg benefit per family reached</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="n">
-        <v>171.4854988887475</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Expected recipients / year</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n">
+        <v>21531.4176</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Expected pregnancies (prenatal)</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n">
+        <v>10765.7088</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Expected infants (postnatal)</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n">
+        <v>10765.7088</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>Avg benefit per recipient</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n">
+        <v>2250</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>Benefits by income quintile → see the 'By income quintile' tab.</t>
         </is>
@@ -699,165 +803,165 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>Quintile</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>Avg income ($)</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>Families</t>
         </is>
       </c>
-      <c r="D1" s="7" t="inlineStr">
-        <is>
-          <t>Families reached</t>
-        </is>
-      </c>
-      <c r="E1" s="7" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
+        <is>
+          <t>Expected recipients</t>
+        </is>
+      </c>
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>Total benefit ($)</t>
         </is>
       </c>
-      <c r="F1" s="7" t="inlineStr">
-        <is>
-          <t>Avg benefit / reached family ($)</t>
-        </is>
-      </c>
-      <c r="G1" s="7" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
+        <is>
+          <t>Avg benefit / recipient ($)</t>
+        </is>
+      </c>
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>Share of benefit (%)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>Q1</t>
         </is>
       </c>
-      <c r="B2" s="9" t="n">
+      <c r="B2" s="11" t="n">
         <v>17164</v>
       </c>
-      <c r="C2" s="9" t="n">
+      <c r="C2" s="11" t="n">
         <v>109745</v>
       </c>
-      <c r="D2" s="9" t="n">
-        <v>99162</v>
-      </c>
-      <c r="E2" s="9" t="n">
-        <v>13391606</v>
-      </c>
-      <c r="F2" s="9" t="n">
-        <v>135</v>
-      </c>
-      <c r="G2" s="10" t="n">
-        <v>25.5</v>
+      <c r="D2" s="11" t="n">
+        <v>5043</v>
+      </c>
+      <c r="E2" s="11" t="n">
+        <v>10482803</v>
+      </c>
+      <c r="F2" s="11" t="n">
+        <v>2079</v>
+      </c>
+      <c r="G2" s="12" t="n">
+        <v>21.6</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>Q2</t>
         </is>
       </c>
-      <c r="B3" s="9" t="n">
+      <c r="B3" s="11" t="n">
         <v>57695</v>
       </c>
-      <c r="C3" s="9" t="n">
+      <c r="C3" s="11" t="n">
         <v>109845</v>
       </c>
-      <c r="D3" s="9" t="n">
-        <v>93305</v>
-      </c>
-      <c r="E3" s="9" t="n">
-        <v>13845924</v>
-      </c>
-      <c r="F3" s="9" t="n">
-        <v>148</v>
-      </c>
-      <c r="G3" s="10" t="n">
-        <v>26.4</v>
+      <c r="D3" s="11" t="n">
+        <v>5583</v>
+      </c>
+      <c r="E3" s="11" t="n">
+        <v>12385737</v>
+      </c>
+      <c r="F3" s="11" t="n">
+        <v>2218</v>
+      </c>
+      <c r="G3" s="12" t="n">
+        <v>25.6</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Q3</t>
         </is>
       </c>
-      <c r="B4" s="9" t="n">
+      <c r="B4" s="11" t="n">
         <v>97780</v>
       </c>
-      <c r="C4" s="9" t="n">
+      <c r="C4" s="11" t="n">
         <v>109868</v>
       </c>
-      <c r="D4" s="9" t="n">
-        <v>41935</v>
-      </c>
-      <c r="E4" s="9" t="n">
-        <v>9117240</v>
-      </c>
-      <c r="F4" s="9" t="n">
-        <v>217</v>
-      </c>
-      <c r="G4" s="10" t="n">
-        <v>17.4</v>
+      <c r="D4" s="11" t="n">
+        <v>4331</v>
+      </c>
+      <c r="E4" s="11" t="n">
+        <v>10904609</v>
+      </c>
+      <c r="F4" s="11" t="n">
+        <v>2518</v>
+      </c>
+      <c r="G4" s="12" t="n">
+        <v>22.5</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Q4</t>
         </is>
       </c>
-      <c r="B5" s="9" t="n">
+      <c r="B5" s="11" t="n">
         <v>155996</v>
       </c>
-      <c r="C5" s="9" t="n">
+      <c r="C5" s="11" t="n">
         <v>109862</v>
       </c>
-      <c r="D5" s="9" t="n">
-        <v>37540</v>
-      </c>
-      <c r="E5" s="9" t="n">
-        <v>8055886</v>
-      </c>
-      <c r="F5" s="9" t="n">
-        <v>215</v>
-      </c>
-      <c r="G5" s="10" t="n">
-        <v>15.3</v>
+      <c r="D5" s="11" t="n">
+        <v>3436</v>
+      </c>
+      <c r="E5" s="11" t="n">
+        <v>7992288</v>
+      </c>
+      <c r="F5" s="11" t="n">
+        <v>2326</v>
+      </c>
+      <c r="G5" s="12" t="n">
+        <v>16.5</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Q5</t>
         </is>
       </c>
-      <c r="B6" s="9" t="n">
+      <c r="B6" s="11" t="n">
         <v>335998</v>
       </c>
-      <c r="C6" s="9" t="n">
+      <c r="C6" s="11" t="n">
         <v>109855</v>
       </c>
-      <c r="D6" s="9" t="n">
-        <v>34469</v>
-      </c>
-      <c r="E6" s="9" t="n">
-        <v>8134387</v>
-      </c>
-      <c r="F6" s="9" t="n">
-        <v>236</v>
-      </c>
-      <c r="G6" s="10" t="n">
-        <v>15.5</v>
+      <c r="D6" s="11" t="n">
+        <v>3138</v>
+      </c>
+      <c r="E6" s="11" t="n">
+        <v>6680254</v>
+      </c>
+      <c r="F6" s="11" t="n">
+        <v>2129</v>
+      </c>
+      <c r="G6" s="12" t="n">
+        <v>13.8</v>
       </c>
     </row>
   </sheetData>
@@ -883,123 +987,123 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>County</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>Cost total ($)</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>Cost prenatal ($)</t>
         </is>
       </c>
-      <c r="D1" s="7" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>Cost postnatal ($)</t>
         </is>
       </c>
-      <c r="E1" s="7" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>Cost SE ($)</t>
         </is>
       </c>
-      <c r="F1" s="7" t="inlineStr">
-        <is>
-          <t>Families reached</t>
+      <c r="F1" s="9" t="inlineStr">
+        <is>
+          <t>Expected recipients</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>Hawaii</t>
         </is>
       </c>
-      <c r="B2" s="9" t="n">
-        <v>8726911</v>
-      </c>
-      <c r="C2" s="9" t="n">
-        <v>5692680</v>
-      </c>
-      <c r="D2" s="9" t="n">
-        <v>3034231</v>
-      </c>
-      <c r="E2" s="9" t="n">
-        <v>502239</v>
-      </c>
-      <c r="F2" s="9" t="n">
-        <v>53432</v>
+      <c r="B2" s="11" t="n">
+        <v>8594218</v>
+      </c>
+      <c r="C2" s="11" t="n">
+        <v>2525755</v>
+      </c>
+      <c r="D2" s="11" t="n">
+        <v>6068462</v>
+      </c>
+      <c r="E2" s="11" t="n">
+        <v>715034</v>
+      </c>
+      <c r="F2" s="11" t="n">
+        <v>3707</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>Honolulu</t>
         </is>
       </c>
-      <c r="B3" s="9" t="n">
-        <v>35862372</v>
-      </c>
-      <c r="C3" s="9" t="n">
-        <v>25203240</v>
-      </c>
-      <c r="D3" s="9" t="n">
-        <v>10659132</v>
-      </c>
-      <c r="E3" s="9" t="n">
-        <v>1099950</v>
-      </c>
-      <c r="F3" s="9" t="n">
-        <v>204292</v>
+      <c r="B3" s="11" t="n">
+        <v>32500557</v>
+      </c>
+      <c r="C3" s="11" t="n">
+        <v>11182293</v>
+      </c>
+      <c r="D3" s="11" t="n">
+        <v>21318264</v>
+      </c>
+      <c r="E3" s="11" t="n">
+        <v>1359266</v>
+      </c>
+      <c r="F3" s="11" t="n">
+        <v>14561</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Kauai</t>
         </is>
       </c>
-      <c r="B4" s="9" t="n">
-        <v>2125810</v>
-      </c>
-      <c r="C4" s="9" t="n">
-        <v>1457520</v>
-      </c>
-      <c r="D4" s="9" t="n">
-        <v>668290</v>
-      </c>
-      <c r="E4" s="9" t="n">
-        <v>266498</v>
-      </c>
-      <c r="F4" s="9" t="n">
-        <v>13359</v>
+      <c r="B4" s="11" t="n">
+        <v>1983259</v>
+      </c>
+      <c r="C4" s="11" t="n">
+        <v>646679</v>
+      </c>
+      <c r="D4" s="11" t="n">
+        <v>1336579</v>
+      </c>
+      <c r="E4" s="11" t="n">
+        <v>329253</v>
+      </c>
+      <c r="F4" s="11" t="n">
+        <v>877</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Maui</t>
         </is>
       </c>
-      <c r="B5" s="9" t="n">
-        <v>5829950</v>
-      </c>
-      <c r="C5" s="9" t="n">
-        <v>4043040</v>
-      </c>
-      <c r="D5" s="9" t="n">
-        <v>1786910</v>
-      </c>
-      <c r="E5" s="9" t="n">
-        <v>454033</v>
-      </c>
-      <c r="F5" s="9" t="n">
-        <v>35328</v>
+      <c r="B5" s="11" t="n">
+        <v>5367656</v>
+      </c>
+      <c r="C5" s="11" t="n">
+        <v>1793835</v>
+      </c>
+      <c r="D5" s="11" t="n">
+        <v>3573821</v>
+      </c>
+      <c r="E5" s="11" t="n">
+        <v>543804</v>
+      </c>
+      <c r="F5" s="11" t="n">
+        <v>2387</v>
       </c>
     </row>
   </sheetData>
@@ -1022,17 +1126,17 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>Parameter</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -1139,15 +1243,15 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Pregnancy probability</t>
+          <t>Pregnancy probability (anchored)</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1</v>
+        <v>0.0444</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Prenatal incidence proxy; swept ±25%</t>
+          <t>Birth-anchored from raw 0.1 so expected pregnancies = eligible births; swept ±25%</t>
         </is>
       </c>
     </row>
@@ -1158,11 +1262,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.033</v>
+        <v>0.066</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Postnatal infant share proxy; swept ±25%</t>
+          <t>Annual births ÷ dependents (FLOW); postnatal infant proxy; swept ±25%</t>
         </is>
       </c>
     </row>
@@ -1250,67 +1354,67 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>RxKids Hawaiʻi — methodology notes (TY 2028)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr"/>
+      <c r="A2" s="14" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Cost = Σ (expected RxKids benefit × household weight) at SPM-unit grain. The benefit is already take-up- and pregnancy-probability-adjusted, so it is an expected annual dollar amount per unit, not a literal payment.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr"/>
+      <c r="A4" s="14" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Household impact here is the distribution of RxKids benefits RECEIVED across weighted income quintiles (SPM units ranked on summed income). This view does not use the tax engine or SPM poverty thresholds, so the whole run is genuine TY2028. A poverty-lift view (persons lifted) would require those engines, which stop at TY2025 — out of scope for this run.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr"/>
+      <c r="A6" s="14" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>Sampling 90% CI is ACS sampling error only (SDR over 80 PUMS replicate weights). The assumption band is a one-at-a-time sweep over the three soft, unanchored parameters (take-up, pregnancy incidence, infant share) — cost is linear in each.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr"/>
+      <c r="A8" s="14" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>The base run prices the 6-month postnatal window (Flint's lower bound). The 'potential' line prices the optional extension to the full 12 months — the program may or may not opt in. Postnatal cost is linear in months, so the additional 6 months roughly equals the base postnatal arm again.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="inlineStr"/>
+      <c r="A10" s="14" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>Caveats: 2026-2028 FPL is CPI-projected off the 2025 HHS table; pregnancy incidence and infant share are held at base-year values.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr"/>
+      <c r="A12" s="14" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>Full methodology: RXKIDS_METHODOLOGY.md (program origin, parameter sourcing, eligibility approximations, limitations).</t>
         </is>

--- a/reports/rxkids_2028/rxkids_2028_cost_and_impact.xlsx
+++ b/reports/rxkids_2028/rxkids_2028_cost_and_impact.xlsx
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>48445689.59999999</v>
+        <v>40954399.2</v>
       </c>
     </row>
     <row r="6">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>16148563.2</v>
+        <v>13651466.4</v>
       </c>
     </row>
     <row r="7">
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>32297126.4</v>
+        <v>27302932.8</v>
       </c>
     </row>
     <row r="8">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>45627472.49774296</v>
+        <v>37989529.63650627</v>
       </c>
     </row>
     <row r="9">
@@ -566,7 +566,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>51263906.70225703</v>
+        <v>43919268.76349373</v>
       </c>
     </row>
     <row r="10">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>1713201.885870538</v>
+        <v>1802352.318233272</v>
       </c>
     </row>
     <row r="11">
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>27250700.4</v>
+        <v>23036849.55</v>
       </c>
     </row>
     <row r="12">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>71911570.5</v>
+        <v>60791686.3125</v>
       </c>
     </row>
     <row r="13">
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>32297126.40000001</v>
+        <v>27302932.8</v>
       </c>
     </row>
     <row r="16">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>80742816</v>
+        <v>68257332</v>
       </c>
     </row>
     <row r="17">
@@ -646,7 +646,7 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>20260465.86666667</v>
+        <v>17127534.23333333</v>
       </c>
     </row>
     <row r="20">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>8747138.4</v>
+        <v>7394544.3</v>
       </c>
     </row>
     <row r="21">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>11513327.46666667</v>
+        <v>9732989.933333334</v>
       </c>
     </row>
     <row r="22">
@@ -676,7 +676,7 @@
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>5980949.333333332</v>
+        <v>5056098.66666667</v>
       </c>
     </row>
     <row r="23">
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>31624269.6</v>
+        <v>26734121.7</v>
       </c>
     </row>
     <row r="25">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>13506977.24444444</v>
+        <v>11418356.15555556</v>
       </c>
     </row>
     <row r="26">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>306411</v>
+        <v>239286</v>
       </c>
     </row>
     <row r="29">
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>21531.4176</v>
+        <v>18201.9552</v>
       </c>
     </row>
     <row r="30">
@@ -746,7 +746,7 @@
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>10765.7088</v>
+        <v>9100.977600000002</v>
       </c>
     </row>
     <row r="31">
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>10765.7088</v>
+        <v>9100.9776</v>
       </c>
     </row>
     <row r="32">
@@ -852,16 +852,16 @@
         <v>109745</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>5043</v>
+        <v>5584</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>10482803</v>
+        <v>11293145</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>2079</v>
+        <v>2023</v>
       </c>
       <c r="G2" s="12" t="n">
-        <v>21.6</v>
+        <v>27.6</v>
       </c>
     </row>
     <row r="3">
@@ -877,16 +877,16 @@
         <v>109845</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>5583</v>
+        <v>6090</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>12385737</v>
+        <v>13146650</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>2218</v>
+        <v>2159</v>
       </c>
       <c r="G3" s="12" t="n">
-        <v>25.6</v>
+        <v>32.1</v>
       </c>
     </row>
     <row r="4">
@@ -902,16 +902,16 @@
         <v>109868</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>4331</v>
+        <v>4270</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>10904609</v>
+        <v>10864331</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>2518</v>
+        <v>2545</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>22.5</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="5">
@@ -927,16 +927,16 @@
         <v>109862</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>3436</v>
+        <v>1932</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>7992288</v>
+        <v>4946859</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>2326</v>
+        <v>2561</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>16.5</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="6">
@@ -952,16 +952,16 @@
         <v>109855</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>3138</v>
+        <v>327</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>6680254</v>
+        <v>703413</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>2129</v>
+        <v>2154</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>13.8</v>
+        <v>1.7</v>
       </c>
     </row>
   </sheetData>
@@ -1025,19 +1025,19 @@
         </is>
       </c>
       <c r="B2" s="11" t="n">
-        <v>8594218</v>
+        <v>8015434</v>
       </c>
       <c r="C2" s="11" t="n">
-        <v>2525755</v>
+        <v>2518003</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>6068462</v>
+        <v>5497430</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>715034</v>
+        <v>791042</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>3707</v>
+        <v>3511</v>
       </c>
     </row>
     <row r="3">
@@ -1047,19 +1047,19 @@
         </is>
       </c>
       <c r="B3" s="11" t="n">
-        <v>32500557</v>
+        <v>26818793</v>
       </c>
       <c r="C3" s="11" t="n">
-        <v>11182293</v>
+        <v>9168756</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>21318264</v>
+        <v>17650037</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>1359266</v>
+        <v>1352049</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>14561</v>
+        <v>11996</v>
       </c>
     </row>
     <row r="4">
@@ -1069,19 +1069,19 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>1983259</v>
+        <v>1703381</v>
       </c>
       <c r="C4" s="11" t="n">
-        <v>646679</v>
+        <v>545794</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>1336579</v>
+        <v>1157587</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>329253</v>
+        <v>315863</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>877</v>
+        <v>750</v>
       </c>
     </row>
     <row r="5">
@@ -1091,19 +1091,19 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>5367656</v>
+        <v>4416792</v>
       </c>
       <c r="C5" s="11" t="n">
-        <v>1793835</v>
+        <v>1418913</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>3573821</v>
+        <v>2997878</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>543804</v>
+        <v>532342</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>2387</v>
+        <v>1945</v>
       </c>
     </row>
   </sheetData>
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0444</v>
+        <v>0.0521</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/reports/rxkids_2028/rxkids_2028_cost_and_impact.xlsx
+++ b/reports/rxkids_2028/rxkids_2028_cost_and_impact.xlsx
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>40954399.2</v>
+        <v>46073699.10000001</v>
       </c>
     </row>
     <row r="6">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>13651466.4</v>
+        <v>15357899.7</v>
       </c>
     </row>
     <row r="7">
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>27302932.8</v>
+        <v>30715799.40000001</v>
       </c>
     </row>
     <row r="8">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>37989529.63650627</v>
+        <v>42738220.84106956</v>
       </c>
     </row>
     <row r="9">
@@ -566,7 +566,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>43919268.76349373</v>
+        <v>49409177.35893046</v>
       </c>
     </row>
     <row r="10">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>1802352.318233272</v>
+        <v>2027646.358012431</v>
       </c>
     </row>
     <row r="11">
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>23036849.55</v>
+        <v>27644219.46</v>
       </c>
     </row>
     <row r="12">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>60791686.3125</v>
+        <v>58743966.35250001</v>
       </c>
     </row>
     <row r="13">
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>27302932.8</v>
+        <v>30715799.39999999</v>
       </c>
     </row>
     <row r="16">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>68257332</v>
+        <v>76789498.5</v>
       </c>
     </row>
     <row r="17">
@@ -646,7 +646,7 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>17127534.23333333</v>
+        <v>19268476.0125</v>
       </c>
     </row>
     <row r="20">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>7394544.3</v>
+        <v>8318862.337499999</v>
       </c>
     </row>
     <row r="21">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>9732989.933333334</v>
+        <v>10949613.675</v>
       </c>
     </row>
     <row r="22">
@@ -676,7 +676,7 @@
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>5056098.66666667</v>
+        <v>5688111</v>
       </c>
     </row>
     <row r="23">
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>26734121.7</v>
+        <v>30075886.9125</v>
       </c>
     </row>
     <row r="25">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>11418356.15555556</v>
+        <v>12845650.675</v>
       </c>
     </row>
     <row r="26">
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>18201.9552</v>
+        <v>20477.1996</v>
       </c>
     </row>
     <row r="30">
@@ -746,7 +746,7 @@
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>9100.977600000002</v>
+        <v>10238.5998</v>
       </c>
     </row>
     <row r="31">
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>9100.9776</v>
+        <v>10238.5998</v>
       </c>
     </row>
     <row r="32">
@@ -852,10 +852,10 @@
         <v>109745</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>5584</v>
+        <v>6281</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>11293145</v>
+        <v>12704789</v>
       </c>
       <c r="F2" s="11" t="n">
         <v>2023</v>
@@ -877,10 +877,10 @@
         <v>109845</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>6090</v>
+        <v>6852</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>13146650</v>
+        <v>14789981</v>
       </c>
       <c r="F3" s="11" t="n">
         <v>2159</v>
@@ -902,10 +902,10 @@
         <v>109868</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>4270</v>
+        <v>4803</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>10864331</v>
+        <v>12222373</v>
       </c>
       <c r="F4" s="11" t="n">
         <v>2545</v>
@@ -927,10 +927,10 @@
         <v>109862</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>1932</v>
+        <v>2173</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>4946859</v>
+        <v>5565216</v>
       </c>
       <c r="F5" s="11" t="n">
         <v>2561</v>
@@ -952,10 +952,10 @@
         <v>109855</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>327</v>
+        <v>367</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>703413</v>
+        <v>791340</v>
       </c>
       <c r="F6" s="11" t="n">
         <v>2154</v>
@@ -1025,19 +1025,19 @@
         </is>
       </c>
       <c r="B2" s="11" t="n">
-        <v>8015434</v>
+        <v>9017363</v>
       </c>
       <c r="C2" s="11" t="n">
-        <v>2518003</v>
+        <v>2832754</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>5497430</v>
+        <v>6184609</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>791042</v>
+        <v>889923</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>3511</v>
+        <v>3950</v>
       </c>
     </row>
     <row r="3">
@@ -1047,19 +1047,19 @@
         </is>
       </c>
       <c r="B3" s="11" t="n">
-        <v>26818793</v>
+        <v>30171142</v>
       </c>
       <c r="C3" s="11" t="n">
-        <v>9168756</v>
+        <v>10314851</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>17650037</v>
+        <v>19856291</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>1352049</v>
+        <v>1521055</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>11996</v>
+        <v>13495</v>
       </c>
     </row>
     <row r="4">
@@ -1069,19 +1069,19 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>1703381</v>
+        <v>1916303</v>
       </c>
       <c r="C4" s="11" t="n">
-        <v>545794</v>
+        <v>614018</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>1157587</v>
+        <v>1302286</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>315863</v>
+        <v>355346</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>750</v>
+        <v>843</v>
       </c>
     </row>
     <row r="5">
@@ -1091,19 +1091,19 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>4416792</v>
+        <v>4968890</v>
       </c>
       <c r="C5" s="11" t="n">
-        <v>1418913</v>
+        <v>1596277</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>2997878</v>
+        <v>3372613</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>532342</v>
+        <v>598884</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>1945</v>
+        <v>2188</v>
       </c>
     </row>
   </sheetData>
@@ -1117,7 +1117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1232,105 +1232,122 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Swept [0.6, 0.95] for the band</t>
+          <t>Combined eligibility×claim (Flint observed 0.98); swept for the band</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Pregnancy probability (anchored)</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>0.0521</v>
+          <t>Fertility response</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>+0%</t>
+        </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Birth-anchored from raw 0.1 so expected pregnancies = eligible births; swept ±25%</t>
+          <t>Induced eligible-birth increase (Flint ~+10%); scales both arms</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Child-under-age share</t>
+          <t>Pregnancy probability (anchored)</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.066</v>
+        <v>0.0521</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Annual births ÷ dependents (FLOW); postnatal infant proxy; swept ±25%</t>
+          <t>Birth-anchored from raw 0.1 so expected pregnancies = eligible births; swept ±25%</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FPL table year</t>
+          <t>Child-under-age share</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2028</v>
+        <v>0.066</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>benefits/_fpl.py (2025 published; 2026-28 CPI-projected)</t>
+          <t>Annual births ÷ dependents (FLOW); postnatal infant proxy; swept ±25%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Tax treatment</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>non-taxable</t>
-        </is>
+          <t>FPL table year</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2028</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Added to SPM resources only; no AGI/EITC/CTC interaction</t>
+          <t>benefits/_fpl.py (2025 published; 2026-28 CPI-projected)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Fiscal weight</t>
+          <t>Tax treatment</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>WGTP (household)</t>
+          <t>non-taxable</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SPM-grain household weight; not the EITC-reweighted tax-unit weight</t>
+          <t>Added to SPM resources only; no AGI/EITC/CTC interaction</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>Fiscal weight</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>WGTP (household)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>SPM-grain household weight; not the EITC-reweighted tax-unit weight</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>Income quintiles</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>WGTP-weighted</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>SPM units ranked on summed income; population-equal fifths</t>
         </is>

--- a/reports/rxkids_2028/rxkids_2028_cost_and_impact.xlsx
+++ b/reports/rxkids_2028/rxkids_2028_cost_and_impact.xlsx
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>46073699.10000001</v>
+        <v>46073699.1</v>
       </c>
     </row>
     <row r="6">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>42738220.84106956</v>
+        <v>41600377.16850201</v>
       </c>
     </row>
     <row r="9">
@@ -566,7 +566,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>49409177.35893046</v>
+        <v>50547021.03149799</v>
       </c>
     </row>
     <row r="10">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>2027646.358012431</v>
+        <v>2719344.639208504</v>
       </c>
     </row>
     <row r="11">
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>30715799.39999999</v>
+        <v>30715799.4</v>
       </c>
     </row>
     <row r="16">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>8318862.337499999</v>
+        <v>8318862.337500001</v>
       </c>
     </row>
     <row r="21">
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>30075886.9125</v>
+        <v>30075886.91250001</v>
       </c>
     </row>
     <row r="25">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>239286</v>
+        <v>80867</v>
       </c>
     </row>
     <row r="29">
@@ -852,16 +852,16 @@
         <v>109745</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>6281</v>
+        <v>4377</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>12704789</v>
+        <v>9847867</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>2023</v>
+        <v>2250</v>
       </c>
       <c r="G2" s="12" t="n">
-        <v>27.6</v>
+        <v>21.4</v>
       </c>
     </row>
     <row r="3">
@@ -877,16 +877,16 @@
         <v>109845</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>6852</v>
+        <v>6017</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>14789981</v>
+        <v>13537408</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>2159</v>
+        <v>2250</v>
       </c>
       <c r="G3" s="12" t="n">
-        <v>32.1</v>
+        <v>29.4</v>
       </c>
     </row>
     <row r="4">
@@ -902,16 +902,16 @@
         <v>109868</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>4803</v>
+        <v>6690</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>12222373</v>
+        <v>15052198</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>2545</v>
+        <v>2250</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>26.5</v>
+        <v>32.7</v>
       </c>
     </row>
     <row r="5">
@@ -927,16 +927,16 @@
         <v>109862</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>2173</v>
+        <v>3074</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>5565216</v>
+        <v>6915586</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>2561</v>
+        <v>2250</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>12.1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
@@ -952,16 +952,16 @@
         <v>109855</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>367</v>
+        <v>320</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>791340</v>
+        <v>720641</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>2154</v>
+        <v>2250</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
     </row>
   </sheetData>
@@ -1025,19 +1025,19 @@
         </is>
       </c>
       <c r="B2" s="11" t="n">
-        <v>9017363</v>
+        <v>9276914</v>
       </c>
       <c r="C2" s="11" t="n">
-        <v>2832754</v>
+        <v>3092305</v>
       </c>
       <c r="D2" s="11" t="n">
         <v>6184609</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>889923</v>
+        <v>1267084</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>3950</v>
+        <v>4123</v>
       </c>
     </row>
     <row r="3">
@@ -1047,19 +1047,19 @@
         </is>
       </c>
       <c r="B3" s="11" t="n">
-        <v>30171142</v>
+        <v>29784437</v>
       </c>
       <c r="C3" s="11" t="n">
-        <v>10314851</v>
+        <v>9928146</v>
       </c>
       <c r="D3" s="11" t="n">
         <v>19856291</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>1521055</v>
+        <v>2017916</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>13495</v>
+        <v>13238</v>
       </c>
     </row>
     <row r="4">
@@ -1069,19 +1069,19 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>1916303</v>
+        <v>1953428</v>
       </c>
       <c r="C4" s="11" t="n">
-        <v>614018</v>
+        <v>651143</v>
       </c>
       <c r="D4" s="11" t="n">
         <v>1302286</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>355346</v>
+        <v>503433</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>843</v>
+        <v>868</v>
       </c>
     </row>
     <row r="5">
@@ -1091,19 +1091,19 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>4968890</v>
+        <v>5058920</v>
       </c>
       <c r="C5" s="11" t="n">
-        <v>1596277</v>
+        <v>1686307</v>
       </c>
       <c r="D5" s="11" t="n">
         <v>3372613</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>598884</v>
+        <v>814645</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>2188</v>
+        <v>2248</v>
       </c>
     </row>
   </sheetData>
@@ -1117,7 +1117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1162,192 +1162,179 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Prenatal unborn count</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1</v>
+          <t>Medicaid OR-clause</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>on</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Family-size increment for the prenatal FPL test</t>
+          <t>Clause 1: medicaid_receives from compute_medicaid_for_units</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Medicaid OR-clause</t>
+          <t>Prenatal payment</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>on</t>
+          <t>$1,500 × 1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Clause 1: medicaid_receives from compute_medicaid_for_units</t>
+          <t>One-time per pregnancy</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Prenatal payment</t>
+          <t>Postnatal payment</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>$1,500 × 1</t>
+          <t>$500/mo × 6</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>One-time per pregnancy</t>
+          <t>Per infant under cutoff</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Postnatal payment</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>$500/mo × 6</t>
-        </is>
+          <t>Take-up rate</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.9</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Per infant under cutoff</t>
+          <t>Combined eligibility×claim (Flint observed 0.98); swept for the band</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Take-up rate</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0.9</v>
+          <t>Fertility response</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>+0%</t>
+        </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Combined eligibility×claim (Flint observed 0.98); swept for the band</t>
+          <t>Induced eligible-birth increase (Flint ~+10%); scales both arms</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Fertility response</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>+0%</t>
-        </is>
+          <t>Birth rate / dependent</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.066</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Induced eligible-birth increase (Flint ~+10%); scales both arms</t>
+          <t>Annual births ÷ dependents (FLOW); drives both arms; swept ±25%</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Pregnancy probability (anchored)</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>0.0521</v>
+          <t>Pregnancy Medicaid pathway</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1.96× FPL</t>
+        </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Birth-anchored from raw 0.1 so expected pregnancies = eligible births; swept ±25%</t>
+          <t>Clause 1 prenatal pathway (196% FPL); subsumed by the 300% income test</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Child-under-age share</t>
+          <t>FPL table year</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.066</v>
+        <v>2028</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Annual births ÷ dependents (FLOW); postnatal infant proxy; swept ±25%</t>
+          <t>benefits/_fpl.py (2025 published; 2026-28 CPI-projected)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FPL table year</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>2028</v>
+          <t>Tax treatment</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>non-taxable</t>
+        </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>benefits/_fpl.py (2025 published; 2026-28 CPI-projected)</t>
+          <t>Added to SPM resources only; no AGI/EITC/CTC interaction</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Tax treatment</t>
+          <t>Fiscal weight</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>non-taxable</t>
+          <t>WGTP (household)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Added to SPM resources only; no AGI/EITC/CTC interaction</t>
+          <t>SPM-grain household weight; not the EITC-reweighted tax-unit weight</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Fiscal weight</t>
+          <t>Income quintiles</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>WGTP (household)</t>
+          <t>WGTP-weighted</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
-        <is>
-          <t>SPM-grain household weight; not the EITC-reweighted tax-unit weight</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Income quintiles</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>WGTP-weighted</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
         <is>
           <t>SPM units ranked on summed income; population-equal fifths</t>
         </is>

--- a/reports/rxkids_2028/rxkids_2028_cost_and_impact.xlsx
+++ b/reports/rxkids_2028/rxkids_2028_cost_and_impact.xlsx
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>46073699.1</v>
+        <v>45436188.60000001</v>
       </c>
     </row>
     <row r="6">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>15357899.7</v>
+        <v>15145396.2</v>
       </c>
     </row>
     <row r="7">
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>30715799.40000001</v>
+        <v>30290792.4</v>
       </c>
     </row>
     <row r="8">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>41600377.16850201</v>
+        <v>41009667.03018691</v>
       </c>
     </row>
     <row r="9">
@@ -566,7 +566,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>50547021.03149799</v>
+        <v>49862710.16981311</v>
       </c>
     </row>
     <row r="10">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>2719344.639208504</v>
+        <v>2690894.571314957</v>
       </c>
     </row>
     <row r="11">
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>27644219.46</v>
+        <v>27261713.16</v>
       </c>
     </row>
     <row r="12">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>58743966.35250001</v>
+        <v>57931140.465</v>
       </c>
     </row>
     <row r="13">
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>30715799.4</v>
+        <v>30290792.39999999</v>
       </c>
     </row>
     <row r="16">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>76789498.5</v>
+        <v>75726981</v>
       </c>
     </row>
     <row r="17">
@@ -646,7 +646,7 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>19268476.0125</v>
+        <v>19001862.825</v>
       </c>
     </row>
     <row r="20">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>8318862.337500001</v>
+        <v>8203756.275</v>
       </c>
     </row>
     <row r="21">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>10949613.675</v>
+        <v>10798106.55</v>
       </c>
     </row>
     <row r="22">
@@ -676,7 +676,7 @@
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>5688111</v>
+        <v>5609406.000000002</v>
       </c>
     </row>
     <row r="23">
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>30075886.91250001</v>
+        <v>29659734.22499999</v>
       </c>
     </row>
     <row r="25">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>12845650.675</v>
+        <v>12667908.55</v>
       </c>
     </row>
     <row r="26">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>80867</v>
+        <v>79842</v>
       </c>
     </row>
     <row r="29">
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>20477.1996</v>
+        <v>20193.8616</v>
       </c>
     </row>
     <row r="30">
@@ -746,7 +746,7 @@
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>10238.5998</v>
+        <v>10096.9308</v>
       </c>
     </row>
     <row r="31">
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>10238.5998</v>
+        <v>10096.9308</v>
       </c>
     </row>
     <row r="32">
@@ -861,7 +861,7 @@
         <v>2250</v>
       </c>
       <c r="G2" s="12" t="n">
-        <v>21.4</v>
+        <v>21.7</v>
       </c>
     </row>
     <row r="3">
@@ -886,7 +886,7 @@
         <v>2250</v>
       </c>
       <c r="G3" s="12" t="n">
-        <v>29.4</v>
+        <v>29.8</v>
       </c>
     </row>
     <row r="4">
@@ -902,16 +902,16 @@
         <v>109868</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>6690</v>
+        <v>6636</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>15052198</v>
+        <v>14930309</v>
       </c>
       <c r="F4" s="11" t="n">
         <v>2250</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>32.7</v>
+        <v>32.9</v>
       </c>
     </row>
     <row r="5">
@@ -927,16 +927,16 @@
         <v>109862</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>3074</v>
+        <v>2952</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>6915586</v>
+        <v>6642138</v>
       </c>
       <c r="F5" s="11" t="n">
         <v>2250</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>15</v>
+        <v>14.6</v>
       </c>
     </row>
     <row r="6">
@@ -952,16 +952,16 @@
         <v>109855</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>320</v>
+        <v>213</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>720641</v>
+        <v>478467</v>
       </c>
       <c r="F6" s="11" t="n">
         <v>2250</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
     </row>
   </sheetData>
@@ -1025,19 +1025,19 @@
         </is>
       </c>
       <c r="B2" s="11" t="n">
-        <v>9276914</v>
+        <v>9211693</v>
       </c>
       <c r="C2" s="11" t="n">
-        <v>3092305</v>
+        <v>3070564</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>6184609</v>
+        <v>6141128</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>1267084</v>
+        <v>1257092</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>4123</v>
+        <v>4094</v>
       </c>
     </row>
     <row r="3">
@@ -1047,19 +1047,19 @@
         </is>
       </c>
       <c r="B3" s="11" t="n">
-        <v>29784437</v>
+        <v>29212148</v>
       </c>
       <c r="C3" s="11" t="n">
-        <v>9928146</v>
+        <v>9737383</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>19856291</v>
+        <v>19474765</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>2017916</v>
+        <v>2025493</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>13238</v>
+        <v>12983</v>
       </c>
     </row>
     <row r="4">

--- a/reports/rxkids_2028/rxkids_2028_cost_and_impact.xlsx
+++ b/reports/rxkids_2028/rxkids_2028_cost_and_impact.xlsx
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>45436188.60000001</v>
+        <v>54399559.50000001</v>
       </c>
     </row>
     <row r="6">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>15145396.2</v>
+        <v>18133186.5</v>
       </c>
     </row>
     <row r="7">
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>30290792.4</v>
+        <v>36266373.00000001</v>
       </c>
     </row>
     <row r="8">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>41009667.03018691</v>
+        <v>50035359.45905797</v>
       </c>
     </row>
     <row r="9">
@@ -566,7 +566,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>49862710.16981311</v>
+        <v>58763759.54094204</v>
       </c>
     </row>
     <row r="10">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>2690894.571314957</v>
+        <v>2653009.14342981</v>
       </c>
     </row>
     <row r="11">
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>27261713.16</v>
+        <v>32639735.70000001</v>
       </c>
     </row>
     <row r="12">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>57931140.465</v>
+        <v>69359438.3625</v>
       </c>
     </row>
     <row r="13">
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>30290792.39999999</v>
+        <v>36266372.99999999</v>
       </c>
     </row>
     <row r="16">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>75726981</v>
+        <v>90665932.5</v>
       </c>
     </row>
     <row r="17">
@@ -646,7 +646,7 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>19001862.825</v>
+        <v>22750433.0625</v>
       </c>
     </row>
     <row r="20">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>8203756.275</v>
+        <v>9822142.687500002</v>
       </c>
     </row>
     <row r="21">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>10798106.55</v>
+        <v>12928290.375</v>
       </c>
     </row>
     <row r="22">
@@ -676,7 +676,7 @@
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>5609406.000000002</v>
+        <v>6715995.000000004</v>
       </c>
     </row>
     <row r="23">
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>29659734.22499999</v>
+        <v>35510823.5625</v>
       </c>
     </row>
     <row r="25">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>12667908.55</v>
+        <v>15166955.375</v>
       </c>
     </row>
     <row r="26">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>79842</v>
+        <v>95919</v>
       </c>
     </row>
     <row r="29">
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>20193.8616</v>
+        <v>24177.582</v>
       </c>
     </row>
     <row r="30">
@@ -746,7 +746,7 @@
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>10096.9308</v>
+        <v>12088.791</v>
       </c>
     </row>
     <row r="31">
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>10096.9308</v>
+        <v>12088.791</v>
       </c>
     </row>
     <row r="32">
@@ -861,7 +861,7 @@
         <v>2250</v>
       </c>
       <c r="G2" s="12" t="n">
-        <v>21.7</v>
+        <v>18.1</v>
       </c>
     </row>
     <row r="3">
@@ -886,7 +886,7 @@
         <v>2250</v>
       </c>
       <c r="G3" s="12" t="n">
-        <v>29.8</v>
+        <v>24.9</v>
       </c>
     </row>
     <row r="4">
@@ -902,16 +902,16 @@
         <v>109868</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>6636</v>
+        <v>6596</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>14930309</v>
+        <v>14842100</v>
       </c>
       <c r="F4" s="11" t="n">
         <v>2250</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>32.9</v>
+        <v>27.3</v>
       </c>
     </row>
     <row r="5">
@@ -927,16 +927,16 @@
         <v>109862</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>2952</v>
+        <v>4232</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>6642138</v>
+        <v>9523097</v>
       </c>
       <c r="F5" s="11" t="n">
         <v>2250</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>14.6</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="6">
@@ -952,16 +952,16 @@
         <v>109855</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>213</v>
+        <v>2955</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>478467</v>
+        <v>6649088</v>
       </c>
       <c r="F6" s="11" t="n">
         <v>2250</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>1.1</v>
+        <v>12.2</v>
       </c>
     </row>
   </sheetData>
@@ -1025,19 +1025,19 @@
         </is>
       </c>
       <c r="B2" s="11" t="n">
-        <v>9211693</v>
+        <v>10240530</v>
       </c>
       <c r="C2" s="11" t="n">
-        <v>3070564</v>
+        <v>3413510</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>6141128</v>
+        <v>6827020</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>1257092</v>
+        <v>1192171</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>4094</v>
+        <v>4551</v>
       </c>
     </row>
     <row r="3">
@@ -1047,19 +1047,19 @@
         </is>
       </c>
       <c r="B3" s="11" t="n">
-        <v>29212148</v>
+        <v>35883688</v>
       </c>
       <c r="C3" s="11" t="n">
-        <v>9737383</v>
+        <v>11961230</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>19474765</v>
+        <v>23922459</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>2025493</v>
+        <v>2109491</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>12983</v>
+        <v>15948</v>
       </c>
     </row>
     <row r="4">
@@ -1069,19 +1069,19 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>1953428</v>
+        <v>2244518</v>
       </c>
       <c r="C4" s="11" t="n">
-        <v>651143</v>
+        <v>748173</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>1302286</v>
+        <v>1496345</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>503433</v>
+        <v>514832</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>868</v>
+        <v>998</v>
       </c>
     </row>
     <row r="5">
@@ -1091,19 +1091,19 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>5058920</v>
+        <v>6030823</v>
       </c>
       <c r="C5" s="11" t="n">
-        <v>1686307</v>
+        <v>2010274</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>3372613</v>
+        <v>4020548</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>814645</v>
+        <v>838695</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>2248</v>
+        <v>2680</v>
       </c>
     </row>
   </sheetData>

--- a/reports/rxkids_2028/rxkids_2028_cost_and_impact.xlsx
+++ b/reports/rxkids_2028/rxkids_2028_cost_and_impact.xlsx
@@ -1351,7 +1351,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1370,7 +1370,7 @@
     <row r="3">
       <c r="A3" s="14" t="inlineStr">
         <is>
-          <t>Cost = Σ (expected RxKids benefit × household weight) at SPM-unit grain. The benefit is already take-up- and pregnancy-probability-adjusted, so it is an expected annual dollar amount per unit, not a literal payment.</t>
+          <t>Both arms are driven by birth events (num_dependents × the annual birth rate per dependent); each eligible birth draws one prenatal + one postnatal payment. Cost = the take-up-adjusted benefit weighted by the household (WGTP) weight, summed to SPM-unit grain. Per-unit amounts are expectations, not literal payments.</t>
         </is>
       </c>
     </row>
@@ -1380,7 +1380,7 @@
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
         <is>
-          <t>Household impact here is the distribution of RxKids benefits RECEIVED across weighted income quintiles (SPM units ranked on summed income). This view does not use the tax engine or SPM poverty thresholds, so the whole run is genuine TY2028. A poverty-lift view (persons lifted) would require those engines, which stop at TY2025 — out of scope for this run.</t>
+          <t>Eligibility is tested on MAGI (gross income with 100% of Social Security) at the tax-unit / MAGI-household grain — the family Medicaid defines (42 CFR 435.603) — consistent with the statute's clause-1 Medicaid anchor. If the bill defines 'family' more broadly, the SPM-family grain (~$45M) is the alternative.</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>Sampling 90% CI is ACS sampling error only (SDR over 80 PUMS replicate weights). The assumption band is a one-at-a-time sweep over the three soft, unanchored parameters (take-up, pregnancy incidence, infant share) — cost is linear in each.</t>
+          <t>Household impact here is the distribution of RxKids benefits RECEIVED across weighted income quintiles (SPM units ranked on summed income). This view does not use the tax engine or SPM poverty thresholds, so the whole run is genuine TY2028. A poverty-lift view (persons lifted) would require those engines, which stop at TY2025 — out of scope for this run.</t>
         </is>
       </c>
     </row>
@@ -1400,7 +1400,7 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>The base run prices the 6-month postnatal window (Flint's lower bound). The 'potential' line prices the optional extension to the full 12 months — the program may or may not opt in. Postnatal cost is linear in months, so the additional 6 months roughly equals the base postnatal arm again.</t>
+          <t>Sampling 90% CI is ACS sampling error only (SDR over 80 PUMS replicate weights). The assumption band is the joint (all-low/all-high corner) sweep over the two soft, unanchored drivers — take-up and the birth rate — cost is linear in each.</t>
         </is>
       </c>
     </row>
@@ -1410,7 +1410,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>Caveats: 2026-2028 FPL is CPI-projected off the 2025 HHS table; pregnancy incidence and infant share are held at base-year values.</t>
+          <t>The base run prices the 6-month postnatal window (Flint's lower bound). The 'potential' line prices the optional extension to the full 12 months — the program may or may not opt in. Postnatal cost is linear in months, so the additional 6 months roughly equals the base postnatal arm again.</t>
         </is>
       </c>
     </row>
@@ -1419,6 +1419,16 @@
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>Caveats: 2026-2028 FPL is CPI-projected off the 2025 HHS table; the birth rate is held at the base-year value (no 2028 birth-trend adjustment).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>Full methodology: RXKIDS_METHODOLOGY.md (program origin, parameter sourcing, eligibility approximations, limitations).</t>
         </is>

--- a/reports/rxkids_2028/rxkids_2028_cost_and_impact.xlsx
+++ b/reports/rxkids_2028/rxkids_2028_cost_and_impact.xlsx
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>54399559.50000001</v>
+        <v>52948904.58000001</v>
       </c>
     </row>
     <row r="6">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>18133186.5</v>
+        <v>16682531.58</v>
       </c>
     </row>
     <row r="7">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>50035359.45905797</v>
+        <v>48701083.20681643</v>
       </c>
     </row>
     <row r="9">
@@ -566,7 +566,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>58763759.54094204</v>
+        <v>57196725.95318358</v>
       </c>
     </row>
     <row r="10">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>2653009.14342981</v>
+        <v>2582262.232938347</v>
       </c>
     </row>
     <row r="11">
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>32639735.70000001</v>
+        <v>31769342.74800001</v>
       </c>
     </row>
     <row r="12">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>69359438.3625</v>
+        <v>67510860.73875001</v>
       </c>
     </row>
     <row r="13">
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>36266372.99999999</v>
+        <v>36266373.00000001</v>
       </c>
     </row>
     <row r="16">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>90665932.5</v>
+        <v>89215277.58000001</v>
       </c>
     </row>
     <row r="17">
@@ -646,7 +646,7 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>22750433.0625</v>
+        <v>21964661.6475</v>
       </c>
     </row>
     <row r="20">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>9822142.687500002</v>
+        <v>9036371.272500001</v>
       </c>
     </row>
     <row r="21">
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="B23" s="8" t="n">
-        <v>41.8</v>
+        <v>41.5</v>
       </c>
     </row>
     <row r="24">
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>35510823.5625</v>
+        <v>34362388.4175</v>
       </c>
     </row>
     <row r="25">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>15166955.375</v>
+        <v>14643107.765</v>
       </c>
     </row>
     <row r="26">
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>24177.582</v>
+        <v>23210.47872</v>
       </c>
     </row>
     <row r="30">
@@ -746,7 +746,7 @@
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>12088.791</v>
+        <v>11121.68772</v>
       </c>
     </row>
     <row r="31">
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="B32" s="6" t="n">
-        <v>2250</v>
+        <v>2281.25</v>
       </c>
     </row>
     <row r="33">
@@ -852,13 +852,13 @@
         <v>109745</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>4377</v>
+        <v>4202</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>9847867</v>
+        <v>9585257</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>2250</v>
+        <v>2281</v>
       </c>
       <c r="G2" s="12" t="n">
         <v>18.1</v>
@@ -877,13 +877,13 @@
         <v>109845</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>6017</v>
+        <v>5776</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>13537408</v>
+        <v>13176411</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>2250</v>
+        <v>2281</v>
       </c>
       <c r="G3" s="12" t="n">
         <v>24.9</v>
@@ -902,13 +902,13 @@
         <v>109868</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>6596</v>
+        <v>6333</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>14842100</v>
+        <v>14446310</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>2250</v>
+        <v>2281</v>
       </c>
       <c r="G4" s="12" t="n">
         <v>27.3</v>
@@ -927,13 +927,13 @@
         <v>109862</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>4232</v>
+        <v>4063</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>9523097</v>
+        <v>9269148</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>2250</v>
+        <v>2281</v>
       </c>
       <c r="G5" s="12" t="n">
         <v>17.5</v>
@@ -952,13 +952,13 @@
         <v>109855</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>2955</v>
+        <v>2837</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>6649088</v>
+        <v>6471779</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>2250</v>
+        <v>2281</v>
       </c>
       <c r="G6" s="12" t="n">
         <v>12.2</v>
@@ -1025,19 +1025,19 @@
         </is>
       </c>
       <c r="B2" s="11" t="n">
-        <v>10240530</v>
+        <v>9967449</v>
       </c>
       <c r="C2" s="11" t="n">
-        <v>3413510</v>
+        <v>3140429</v>
       </c>
       <c r="D2" s="11" t="n">
         <v>6827020</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>1192171</v>
+        <v>1160380</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>4551</v>
+        <v>4369</v>
       </c>
     </row>
     <row r="3">
@@ -1047,19 +1047,19 @@
         </is>
       </c>
       <c r="B3" s="11" t="n">
-        <v>35883688</v>
+        <v>34926790</v>
       </c>
       <c r="C3" s="11" t="n">
-        <v>11961230</v>
+        <v>11004331</v>
       </c>
       <c r="D3" s="11" t="n">
         <v>23922459</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>2109491</v>
+        <v>2053238</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>15948</v>
+        <v>15310</v>
       </c>
     </row>
     <row r="4">
@@ -1069,19 +1069,19 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>2244518</v>
+        <v>2184664</v>
       </c>
       <c r="C4" s="11" t="n">
-        <v>748173</v>
+        <v>688319</v>
       </c>
       <c r="D4" s="11" t="n">
         <v>1496345</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>514832</v>
+        <v>501103</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>998</v>
+        <v>958</v>
       </c>
     </row>
     <row r="5">
@@ -1091,19 +1091,19 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>6030823</v>
+        <v>5870001</v>
       </c>
       <c r="C5" s="11" t="n">
-        <v>2010274</v>
+        <v>1849452</v>
       </c>
       <c r="D5" s="11" t="n">
         <v>4020548</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>838695</v>
+        <v>816330</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>2680</v>
+        <v>2573</v>
       </c>
     </row>
   </sheetData>
@@ -1117,7 +1117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1213,7 +1213,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Take-up rate</t>
+          <t>Take-up — postnatal (newborn)</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -1221,120 +1221,135 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Combined eligibility×claim (Flint observed 0.98); swept for the band</t>
+          <t>Flint observed 0.98; swept for the band</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Fertility response</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>+0%</t>
-        </is>
+          <t>Take-up — prenatal</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.828</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Induced eligible-birth increase (Flint ~+10%); scales both arms</t>
+          <t>0.92× postnatal (Flint: ~90% prenatal vs 98% newborn)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Birth rate / dependent</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>0.066</v>
+          <t>Fertility response</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>+0%</t>
+        </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Annual births ÷ dependents (FLOW); drives both arms; swept ±25%</t>
+          <t>Induced eligible-birth increase (Flint ~+10%); scales both arms</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Pregnancy Medicaid pathway</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>1.96× FPL</t>
-        </is>
+          <t>Birth rate / dependent</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.066</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Clause 1 prenatal pathway (196% FPL); subsumed by the 300% income test</t>
+          <t>Annual births ÷ dependents (FLOW); drives both arms; swept ±25%</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FPL table year</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>2028</v>
+          <t>Pregnancy Medicaid pathway</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1.96× FPL</t>
+        </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>benefits/_fpl.py (2025 published; 2026-28 CPI-projected)</t>
+          <t>Clause 1 prenatal pathway (196% FPL); subsumed by the 300% income test</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Tax treatment</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>non-taxable</t>
-        </is>
+          <t>FPL table year</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2028</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Added to SPM resources only; no AGI/EITC/CTC interaction</t>
+          <t>benefits/_fpl.py (2025 published; 2026-28 CPI-projected)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Fiscal weight</t>
+          <t>Tax treatment</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>WGTP (household)</t>
+          <t>non-taxable</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SPM-grain household weight; not the EITC-reweighted tax-unit weight</t>
+          <t>Added to SPM resources only; no AGI/EITC/CTC interaction</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>Fiscal weight</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>WGTP (household)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>SPM-grain household weight; not the EITC-reweighted tax-unit weight</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>Income quintiles</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>WGTP-weighted</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>SPM units ranked on summed income; population-equal fifths</t>
         </is>

--- a/reports/rxkids_2028/rxkids_2028_cost_and_impact.xlsx
+++ b/reports/rxkids_2028/rxkids_2028_cost_and_impact.xlsx
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B34"/>
+  <dimension ref="A1:B36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -522,11 +522,11 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Total program cost</t>
+          <t>Total program cost (benefit)</t>
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>52948904.58000001</v>
+        <v>28872688.66182907</v>
       </c>
     </row>
     <row r="6">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>16682531.58</v>
+        <v>9096874.509891348</v>
       </c>
     </row>
     <row r="7">
@@ -546,234 +546,254 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>36266373.00000001</v>
+        <v>19775814.15193772</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>Sampling 90% CI — low</t>
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Administrative load (8%)</t>
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>48701083.20681643</v>
+        <v>2309815.092946325</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Sampling 90% CI — high</t>
+          <t>Appropriation total (benefit + admin)</t>
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>57196725.95318358</v>
+        <v>31182503.75477539</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  SDR standard error</t>
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Sampling 90% CI — low</t>
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>2582262.232938347</v>
+        <v>25694992.58087159</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
+          <t>Sampling 90% CI — high</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>32050384.74278655</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  SDR standard error</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>1931730.140399683</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
           <t>Assumption band — low</t>
         </is>
       </c>
-      <c r="B11" s="6" t="n">
-        <v>31769342.74800001</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="B13" s="6" t="n">
+        <v>17323613.19709744</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>Assumption band — high</t>
         </is>
       </c>
-      <c r="B12" s="6" t="n">
-        <v>67510860.73875001</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="B14" s="6" t="n">
+        <v>36813227.37200294</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>POTENTIAL — extend postnatal 6→12 months (optional)</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Additional cost (+6 months)</t>
         </is>
       </c>
-      <c r="B15" s="6" t="n">
-        <v>36266373.00000001</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="B17" s="6" t="n">
+        <v>19775814.15193772</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Total cost (12-month design)</t>
         </is>
       </c>
-      <c r="B16" s="6" t="n">
-        <v>89215277.58000001</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="B18" s="6" t="n">
+        <v>48648502.81376678</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>FIRST FISCAL YEAR (launch) — 12mo operating, 12mo ramp</t>
         </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Year-1 disbursement (total)</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="n">
-        <v>21964661.6475</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Prenatal</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="n">
-        <v>9036371.272500001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Postnatal</t>
+          <t xml:space="preserve">  Year-1 disbursement (total)</t>
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>12928290.375</v>
+        <v>11977185.21924302</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    (postnatal deferred to next FY)</t>
+          <t xml:space="preserve">    Prenatal</t>
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>6715995.000000004</v>
+        <v>4927473.692857813</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Year-1 as % of steady state</t>
-        </is>
-      </c>
-      <c r="B23" s="8" t="n">
-        <v>41.5</v>
+          <t xml:space="preserve">    Postnatal</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n">
+        <v>7049711.526385205</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Year-1 if ramp = 6mo (fast)</t>
+          <t xml:space="preserve">    (postnatal deferred to next FY)</t>
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>34362388.4175</v>
+        <v>3662187.805914393</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">  Year-1 as % of steady state</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="n">
+        <v>41.5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Year-1 if ramp = 6mo (fast)</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n">
+        <v>18737583.90896099</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">  Year-1 if ramp = 18mo (slow)</t>
         </is>
       </c>
-      <c r="B25" s="6" t="n">
-        <v>14643107.765</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="B27" s="6" t="n">
+        <v>7984790.146162013</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>HOUSEHOLD REACH</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>Eligible families (weighted)</t>
         </is>
       </c>
-      <c r="B28" s="6" t="n">
-        <v>95919</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="B30" s="6" t="n">
+        <v>7988</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>Expected recipients / year</t>
         </is>
       </c>
-      <c r="B29" s="6" t="n">
-        <v>23210.47872</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="7" t="inlineStr">
+      <c r="B31" s="6" t="n">
+        <v>12656.52105724014</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Expected pregnancies (prenatal)</t>
         </is>
       </c>
-      <c r="B30" s="6" t="n">
-        <v>11121.68772</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="7" t="inlineStr">
+      <c r="B32" s="6" t="n">
+        <v>6064.583006594232</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Expected infants (postnatal)</t>
         </is>
       </c>
-      <c r="B31" s="6" t="n">
-        <v>12088.791</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+      <c r="B33" s="6" t="n">
+        <v>6591.938050645906</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>Avg benefit per recipient</t>
         </is>
       </c>
-      <c r="B32" s="6" t="n">
+      <c r="B34" s="6" t="n">
         <v>2281.25</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>Benefits by income quintile → see the 'By income quintile' tab.</t>
         </is>
@@ -846,22 +866,22 @@
         </is>
       </c>
       <c r="B2" s="11" t="n">
-        <v>17164</v>
+        <v>15550</v>
       </c>
       <c r="C2" s="11" t="n">
-        <v>109745</v>
+        <v>106603</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>4202</v>
+        <v>1983</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>9585257</v>
+        <v>4523446</v>
       </c>
       <c r="F2" s="11" t="n">
         <v>2281</v>
       </c>
       <c r="G2" s="12" t="n">
-        <v>18.1</v>
+        <v>15.7</v>
       </c>
     </row>
     <row r="3">
@@ -871,22 +891,22 @@
         </is>
       </c>
       <c r="B3" s="11" t="n">
-        <v>57695</v>
+        <v>53369</v>
       </c>
       <c r="C3" s="11" t="n">
-        <v>109845</v>
+        <v>106692</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>5776</v>
+        <v>4013</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>13176411</v>
+        <v>9154925</v>
       </c>
       <c r="F3" s="11" t="n">
         <v>2281</v>
       </c>
       <c r="G3" s="12" t="n">
-        <v>24.9</v>
+        <v>31.7</v>
       </c>
     </row>
     <row r="4">
@@ -896,16 +916,16 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>97780</v>
+        <v>93190</v>
       </c>
       <c r="C4" s="11" t="n">
-        <v>109868</v>
+        <v>106664</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>6333</v>
+        <v>3454</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>14446310</v>
+        <v>7879439</v>
       </c>
       <c r="F4" s="11" t="n">
         <v>2281</v>
@@ -921,22 +941,22 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>155996</v>
+        <v>147826</v>
       </c>
       <c r="C5" s="11" t="n">
-        <v>109862</v>
+        <v>106653</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>4063</v>
+        <v>2386</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>9269148</v>
+        <v>5443469</v>
       </c>
       <c r="F5" s="11" t="n">
         <v>2281</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>17.5</v>
+        <v>18.9</v>
       </c>
     </row>
     <row r="6">
@@ -946,22 +966,22 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>335998</v>
+        <v>309577</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>109855</v>
+        <v>106656</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>2837</v>
+        <v>820</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>6471779</v>
+        <v>1871410</v>
       </c>
       <c r="F6" s="11" t="n">
         <v>2281</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>12.2</v>
+        <v>6.5</v>
       </c>
     </row>
   </sheetData>
@@ -1025,19 +1045,19 @@
         </is>
       </c>
       <c r="B2" s="11" t="n">
-        <v>9967449</v>
+        <v>4181922</v>
       </c>
       <c r="C2" s="11" t="n">
-        <v>3140429</v>
+        <v>1317592</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>6827020</v>
+        <v>2864330</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>1160380</v>
+        <v>843997</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>4369</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="3">
@@ -1047,19 +1067,19 @@
         </is>
       </c>
       <c r="B3" s="11" t="n">
-        <v>34926790</v>
+        <v>19602761</v>
       </c>
       <c r="C3" s="11" t="n">
-        <v>11004331</v>
+        <v>6176212</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>23922459</v>
+        <v>13426549</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>2053238</v>
+        <v>1498925</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>15310</v>
+        <v>8593</v>
       </c>
     </row>
     <row r="4">
@@ -1069,19 +1089,19 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>2184664</v>
+        <v>829415</v>
       </c>
       <c r="C4" s="11" t="n">
-        <v>688319</v>
+        <v>261322</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>1496345</v>
+        <v>568092</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>501103</v>
+        <v>221813</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>958</v>
+        <v>364</v>
       </c>
     </row>
     <row r="5">
@@ -1091,19 +1111,19 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>5870001</v>
+        <v>4258591</v>
       </c>
       <c r="C5" s="11" t="n">
-        <v>1849452</v>
+        <v>1341748</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>4020548</v>
+        <v>2916843</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>816330</v>
+        <v>666380</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>2573</v>
+        <v>1867</v>
       </c>
     </row>
   </sheetData>
@@ -1117,7 +1137,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1260,96 +1280,132 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Birth rate / dependent</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>0.066</v>
+          <t>Birth driver</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>observed (age-0 deps)</t>
+        </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Annual births ÷ dependents (FLOW); drives both arms; swept ±25%</t>
+          <t>Observed: age-0 dependents in PUMS, calibrated to NVSR; drives both arms; swept ±25%</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Pregnancy Medicaid pathway</t>
+          <t>Birth cohort — base / target</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1.96× FPL</t>
+          <t>15,419 -&gt; 13,632</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Clause 1 prenatal pathway (196% FPL); subsumed by the 300% income test</t>
+          <t>NVSR 2022 basis; ensemble-projected to 2028</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FPL table year</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>2028</v>
+          <t>Administrative load</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>8%</t>
+        </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>benefits/_fpl.py (2025 published; 2026-28 CPI-projected)</t>
+          <t>Operating overhead on benefit cost; separate appropriation line</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Tax treatment</t>
+          <t>Pregnancy Medicaid pathway</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>non-taxable</t>
+          <t>1.96× FPL</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Added to SPM resources only; no AGI/EITC/CTC interaction</t>
+          <t>Clause 1 prenatal pathway (196% FPL); subsumed by the 300% income test</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Fiscal weight</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>WGTP (household)</t>
-        </is>
+          <t>FPL table year</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2028</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SPM-grain household weight; not the EITC-reweighted tax-unit weight</t>
+          <t>benefits/_fpl.py (2025 published; 2026-28 CPI-projected)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>Tax treatment</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>non-taxable</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Added to SPM resources only; no AGI/EITC/CTC interaction</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Fiscal weight</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>WGTP (household)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>SPM-grain household weight; not the EITC-reweighted tax-unit weight</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>Income quintiles</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>WGTP-weighted</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>SPM units ranked on summed income; population-equal fifths</t>
         </is>
@@ -1366,7 +1422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1385,7 +1441,7 @@
     <row r="3">
       <c r="A3" s="14" t="inlineStr">
         <is>
-          <t>Both arms are driven by birth events (num_dependents × the annual birth rate per dependent); each eligible birth draws one prenatal + one postnatal payment. Cost = the take-up-adjusted benefit weighted by the household (WGTP) weight, summed to SPM-unit grain. Per-unit amounts are expectations, not literal payments.</t>
+          <t>Both arms are driven by OBSERVED births — the count of age-0 dependents in each PUMS tax unit (an infant &lt;1yr ≈ a birth in the last 12 months, the annual flow). The weighted count is calibrated to CDC NVSR resident births (by-residence basis, 2022=15,535), then projected to 2028 with the repo's damped-trend ensemble (point 13,632, 90% PI [10,502, 16,761]). Each birth draws one prenatal + one postnatal payment. This replaces the legacy num_dependents × rate proxy, which multiplied an all-dependents count (incl. older children, students, adult dependents) by a children-only-calibrated rate and overstated total births ~1.7×. Cost = the take-up-adjusted benefit weighted by the household (WGTP) weight, summed to SPM-unit grain. Per-unit amounts are expectations, not literal payments.</t>
         </is>
       </c>
     </row>
@@ -1415,7 +1471,7 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>Sampling 90% CI is ACS sampling error only (SDR over 80 PUMS replicate weights). The assumption band is the joint (all-low/all-high corner) sweep over the two soft, unanchored drivers — take-up and the birth rate — cost is linear in each.</t>
+          <t>Sampling 90% CI is ACS sampling error only (SDR over 80 PUMS replicate weights). The assumption band is the joint (all-low/all-high corner) sweep over the two soft drivers — take-up and the birth count (±25%) — cost is linear in each. The ±25% birth band comfortably covers the ensemble birth-projection's ~±23% 90% PI.</t>
         </is>
       </c>
     </row>
@@ -1425,7 +1481,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>The base run prices the 6-month postnatal window (Flint's lower bound). The 'potential' line prices the optional extension to the full 12 months — the program may or may not opt in. Postnatal cost is linear in months, so the additional 6 months roughly equals the base postnatal arm again.</t>
+          <t>The reported program cost is benefit dollars (cash out the door). The administrative line (8% of benefit) covers operating overhead (enrollment, disbursement, eligibility, outreach); the appropriation total is benefit + admin.</t>
         </is>
       </c>
     </row>
@@ -1435,7 +1491,7 @@
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>Caveats: 2026-2028 FPL is CPI-projected off the 2025 HHS table; the birth rate is held at the base-year value (no 2028 birth-trend adjustment).</t>
+          <t>The base run prices the 6-month postnatal window (Flint's lower bound). The 'potential' line prices the optional extension to the full 12 months — the program may or may not opt in. Postnatal cost is linear in months, so the additional 6 months roughly equals the base postnatal arm again.</t>
         </is>
       </c>
     </row>
@@ -1444,6 +1500,16 @@
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>Caveats: 2026-2028 FPL is CPI-projected off the 2025 HHS table. The birth cohort is projected with the ensemble (vital-statistics counts, not survey estimates); update HI_BIRTHS_BY_YEAR as new NVSR final-data releases land.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="14" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>Full methodology: RXKIDS_METHODOLOGY.md (program origin, parameter sourcing, eligibility approximations, limitations).</t>
         </is>

--- a/reports/rxkids_2028/rxkids_2028_cost_and_impact.xlsx
+++ b/reports/rxkids_2028/rxkids_2028_cost_and_impact.xlsx
@@ -10,8 +10,10 @@
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="By income quintile" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="By county" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Assumptions" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Notes" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="By scenario" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="County x scenario" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Assumptions" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Notes" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +528,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>28872688.66182907</v>
+        <v>32087983.0824431</v>
       </c>
     </row>
     <row r="6">
@@ -536,7 +538,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>9096874.509891348</v>
+        <v>10109912.47803002</v>
       </c>
     </row>
     <row r="7">
@@ -546,7 +548,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>19775814.15193772</v>
+        <v>21978070.60441308</v>
       </c>
     </row>
     <row r="8">
@@ -556,7 +558,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>2309815.092946325</v>
+        <v>2567038.646595448</v>
       </c>
     </row>
     <row r="9">
@@ -566,7 +568,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>31182503.75477539</v>
+        <v>34655021.72903854</v>
       </c>
     </row>
     <row r="10">
@@ -576,7 +578,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>25694992.58087159</v>
+        <v>28633407.51224043</v>
       </c>
     </row>
     <row r="11">
@@ -586,7 +588,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>32050384.74278655</v>
+        <v>35542558.65264577</v>
       </c>
     </row>
     <row r="12">
@@ -596,7 +598,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>1931730.140399683</v>
+        <v>2100045.93933293</v>
       </c>
     </row>
     <row r="13">
@@ -606,7 +608,7 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>17323613.19709744</v>
+        <v>19252789.84946586</v>
       </c>
     </row>
     <row r="14">
@@ -616,7 +618,7 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>36813227.37200294</v>
+        <v>40912788.93207619</v>
       </c>
     </row>
     <row r="15">
@@ -636,7 +638,7 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>19775814.15193772</v>
+        <v>21978070.60441308</v>
       </c>
     </row>
     <row r="18">
@@ -646,7 +648,7 @@
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>48648502.81376678</v>
+        <v>54066053.68685618</v>
       </c>
     </row>
     <row r="19">
@@ -666,7 +668,7 @@
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>11977185.21924302</v>
+        <v>13310977.76143204</v>
       </c>
     </row>
     <row r="22">
@@ -676,7 +678,7 @@
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>4927473.692857813</v>
+        <v>5476202.59226626</v>
       </c>
     </row>
     <row r="23">
@@ -686,7 +688,7 @@
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>7049711.526385205</v>
+        <v>7834775.169165776</v>
       </c>
     </row>
     <row r="24">
@@ -696,7 +698,7 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>3662187.805914393</v>
+        <v>4070013.074891313</v>
       </c>
     </row>
     <row r="25">
@@ -716,7 +718,7 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>18737583.90896099</v>
+        <v>20824221.89768139</v>
       </c>
     </row>
     <row r="27">
@@ -726,7 +728,7 @@
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>7984790.146162013</v>
+        <v>8873985.174288023</v>
       </c>
     </row>
     <row r="28">
@@ -746,7 +748,7 @@
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>7988</v>
+        <v>8158</v>
       </c>
     </row>
     <row r="31">
@@ -756,7 +758,7 @@
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>12656.52105724014</v>
+        <v>14065.96518682437</v>
       </c>
     </row>
     <row r="32">
@@ -766,7 +768,7 @@
         </is>
       </c>
       <c r="B32" s="6" t="n">
-        <v>6064.583006594232</v>
+        <v>6739.941652020011</v>
       </c>
     </row>
     <row r="33">
@@ -776,7 +778,7 @@
         </is>
       </c>
       <c r="B33" s="6" t="n">
-        <v>6591.938050645906</v>
+        <v>7326.023534804361</v>
       </c>
     </row>
     <row r="34">
@@ -866,22 +868,22 @@
         </is>
       </c>
       <c r="B2" s="11" t="n">
-        <v>15550</v>
+        <v>15315</v>
       </c>
       <c r="C2" s="11" t="n">
-        <v>106603</v>
+        <v>107149</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>1983</v>
+        <v>2230</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>4523446</v>
+        <v>5087073</v>
       </c>
       <c r="F2" s="11" t="n">
         <v>2281</v>
       </c>
       <c r="G2" s="12" t="n">
-        <v>15.7</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="3">
@@ -891,22 +893,22 @@
         </is>
       </c>
       <c r="B3" s="11" t="n">
-        <v>53369</v>
+        <v>52619</v>
       </c>
       <c r="C3" s="11" t="n">
-        <v>106692</v>
+        <v>107150</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>4013</v>
+        <v>4377</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>9154925</v>
+        <v>9984613</v>
       </c>
       <c r="F3" s="11" t="n">
         <v>2281</v>
       </c>
       <c r="G3" s="12" t="n">
-        <v>31.7</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="4">
@@ -916,22 +918,22 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>93190</v>
+        <v>92200</v>
       </c>
       <c r="C4" s="11" t="n">
-        <v>106664</v>
+        <v>107159</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>3454</v>
+        <v>3745</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>7879439</v>
+        <v>8544160</v>
       </c>
       <c r="F4" s="11" t="n">
         <v>2281</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>27.3</v>
+        <v>26.6</v>
       </c>
     </row>
     <row r="5">
@@ -941,22 +943,22 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>147826</v>
+        <v>146436</v>
       </c>
       <c r="C5" s="11" t="n">
-        <v>106653</v>
+        <v>107149</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>2386</v>
+        <v>2690</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>5443469</v>
+        <v>6137087</v>
       </c>
       <c r="F5" s="11" t="n">
         <v>2281</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>18.9</v>
+        <v>19.1</v>
       </c>
     </row>
     <row r="6">
@@ -966,22 +968,22 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>309577</v>
+        <v>307932</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>106656</v>
+        <v>107157</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>820</v>
+        <v>1024</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>1871410</v>
+        <v>2335050</v>
       </c>
       <c r="F6" s="11" t="n">
         <v>2281</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>6.5</v>
+        <v>7.3</v>
       </c>
     </row>
   </sheetData>
@@ -1045,19 +1047,19 @@
         </is>
       </c>
       <c r="B2" s="11" t="n">
-        <v>4181922</v>
+        <v>4609449</v>
       </c>
       <c r="C2" s="11" t="n">
-        <v>1317592</v>
+        <v>1452292</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>2864330</v>
+        <v>3157157</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>843997</v>
+        <v>907555</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>1833</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="3">
@@ -1067,19 +1069,19 @@
         </is>
       </c>
       <c r="B3" s="11" t="n">
-        <v>19602761</v>
+        <v>21932790</v>
       </c>
       <c r="C3" s="11" t="n">
-        <v>6176212</v>
+        <v>6910331</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>13426549</v>
+        <v>15022459</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>1498925</v>
+        <v>1594676</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>8593</v>
+        <v>9614</v>
       </c>
     </row>
     <row r="4">
@@ -1089,19 +1091,19 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>829415</v>
+        <v>1057596</v>
       </c>
       <c r="C4" s="11" t="n">
-        <v>261322</v>
+        <v>333215</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>568092</v>
+        <v>724381</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>221813</v>
+        <v>271196</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>364</v>
+        <v>464</v>
       </c>
     </row>
     <row r="5">
@@ -1111,19 +1113,19 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>4258591</v>
+        <v>4488148</v>
       </c>
       <c r="C5" s="11" t="n">
-        <v>1341748</v>
+        <v>1414074</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>2916843</v>
+        <v>3074074</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>666380</v>
+        <v>731413</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>1867</v>
+        <v>1967</v>
       </c>
     </row>
   </sheetData>
@@ -1132,6 +1134,643 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Scenario comparison — take-up held constant (0.90 newborn / 0.83 prenatal); only eligibility + postnatal months differ</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="B2" s="9" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>Postnatal mo</t>
+        </is>
+      </c>
+      <c r="D2" s="9" t="inlineStr">
+        <is>
+          <t>$/birth</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="inlineStr">
+        <is>
+          <t>Cost total ($)</t>
+        </is>
+      </c>
+      <c r="F2" s="9" t="inlineStr">
+        <is>
+          <t>Prenatal ($)</t>
+        </is>
+      </c>
+      <c r="G2" s="9" t="inlineStr">
+        <is>
+          <t>Postnatal ($)</t>
+        </is>
+      </c>
+      <c r="H2" s="9" t="inlineStr">
+        <is>
+          <t>Admin ($)</t>
+        </is>
+      </c>
+      <c r="I2" s="9" t="inlineStr">
+        <is>
+          <t>Appropriation ($)</t>
+        </is>
+      </c>
+      <c r="J2" s="9" t="inlineStr">
+        <is>
+          <t>Band low ($)</t>
+        </is>
+      </c>
+      <c r="K2" s="9" t="inlineStr">
+        <is>
+          <t>Band high ($)</t>
+        </is>
+      </c>
+      <c r="L2" s="9" t="inlineStr">
+        <is>
+          <t>Expected recipients</t>
+        </is>
+      </c>
+      <c r="M2" s="9" t="inlineStr">
+        <is>
+          <t>Avg benefit ($)</t>
+        </is>
+      </c>
+      <c r="N2" s="9" t="inlineStr">
+        <is>
+          <t>First-year ($)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>Statutory (Medicaid OR ≤300% FPL) · 6-mo postnatal</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>Medicaid OR ≤300% FPL</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="D3" s="11" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E3" s="11" t="n">
+        <v>32087983</v>
+      </c>
+      <c r="F3" s="11" t="n">
+        <v>10109912</v>
+      </c>
+      <c r="G3" s="11" t="n">
+        <v>21978071</v>
+      </c>
+      <c r="H3" s="11" t="n">
+        <v>2567039</v>
+      </c>
+      <c r="I3" s="11" t="n">
+        <v>34655022</v>
+      </c>
+      <c r="J3" s="11" t="n">
+        <v>19252790</v>
+      </c>
+      <c r="K3" s="11" t="n">
+        <v>40912789</v>
+      </c>
+      <c r="L3" s="11" t="n">
+        <v>14066</v>
+      </c>
+      <c r="M3" s="11" t="n">
+        <v>2281</v>
+      </c>
+      <c r="N3" s="11" t="n">
+        <v>13310978</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>Universal · 6-mo postnatal</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>Universal (no income/Medicaid test)</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="D4" s="11" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E4" s="11" t="n">
+        <v>49801763</v>
+      </c>
+      <c r="F4" s="11" t="n">
+        <v>15690966</v>
+      </c>
+      <c r="G4" s="11" t="n">
+        <v>34110796</v>
+      </c>
+      <c r="H4" s="11" t="n">
+        <v>3984141</v>
+      </c>
+      <c r="I4" s="11" t="n">
+        <v>53785904</v>
+      </c>
+      <c r="J4" s="11" t="n">
+        <v>29881058</v>
+      </c>
+      <c r="K4" s="11" t="n">
+        <v>63498195</v>
+      </c>
+      <c r="L4" s="11" t="n">
+        <v>21831</v>
+      </c>
+      <c r="M4" s="11" t="n">
+        <v>2281</v>
+      </c>
+      <c r="N4" s="11" t="n">
+        <v>20659141</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>Universal · 12-mo postnatal</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>Universal (no income/Medicaid test)</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D5" s="11" t="n">
+        <v>7500</v>
+      </c>
+      <c r="E5" s="11" t="n">
+        <v>83912559</v>
+      </c>
+      <c r="F5" s="11" t="n">
+        <v>15690966</v>
+      </c>
+      <c r="G5" s="11" t="n">
+        <v>68221593</v>
+      </c>
+      <c r="H5" s="11" t="n">
+        <v>6713005</v>
+      </c>
+      <c r="I5" s="11" t="n">
+        <v>90625564</v>
+      </c>
+      <c r="J5" s="11" t="n">
+        <v>50347535</v>
+      </c>
+      <c r="K5" s="11" t="n">
+        <v>106989460</v>
+      </c>
+      <c r="L5" s="11" t="n">
+        <v>21831</v>
+      </c>
+      <c r="M5" s="11" t="n">
+        <v>3844</v>
+      </c>
+      <c r="N5" s="11" t="n">
+        <v>22870026</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="inlineStr">
+        <is>
+          <t>County</t>
+        </is>
+      </c>
+      <c r="C1" s="9" t="inlineStr">
+        <is>
+          <t>Cost total ($)</t>
+        </is>
+      </c>
+      <c r="D1" s="9" t="inlineStr">
+        <is>
+          <t>Cost prenatal ($)</t>
+        </is>
+      </c>
+      <c r="E1" s="9" t="inlineStr">
+        <is>
+          <t>Cost postnatal ($)</t>
+        </is>
+      </c>
+      <c r="F1" s="9" t="inlineStr">
+        <is>
+          <t>Cost SE ($)</t>
+        </is>
+      </c>
+      <c r="G1" s="9" t="inlineStr">
+        <is>
+          <t>Expected recipients</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>Statutory (Medicaid OR ≤300% FPL) · 6-mo postnatal</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="C2" s="11" t="n">
+        <v>4609449</v>
+      </c>
+      <c r="D2" s="11" t="n">
+        <v>1452292</v>
+      </c>
+      <c r="E2" s="11" t="n">
+        <v>3157157</v>
+      </c>
+      <c r="F2" s="11" t="n">
+        <v>907555</v>
+      </c>
+      <c r="G2" s="11" t="n">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>Statutory (Medicaid OR ≤300% FPL) · 6-mo postnatal</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>Honolulu</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="n">
+        <v>21932790</v>
+      </c>
+      <c r="D3" s="11" t="n">
+        <v>6910331</v>
+      </c>
+      <c r="E3" s="11" t="n">
+        <v>15022459</v>
+      </c>
+      <c r="F3" s="11" t="n">
+        <v>1594676</v>
+      </c>
+      <c r="G3" s="11" t="n">
+        <v>9614</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>Statutory (Medicaid OR ≤300% FPL) · 6-mo postnatal</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>Kauai</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="n">
+        <v>1057596</v>
+      </c>
+      <c r="D4" s="11" t="n">
+        <v>333215</v>
+      </c>
+      <c r="E4" s="11" t="n">
+        <v>724381</v>
+      </c>
+      <c r="F4" s="11" t="n">
+        <v>271196</v>
+      </c>
+      <c r="G4" s="11" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>Statutory (Medicaid OR ≤300% FPL) · 6-mo postnatal</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>Maui</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="n">
+        <v>4488148</v>
+      </c>
+      <c r="D5" s="11" t="n">
+        <v>1414074</v>
+      </c>
+      <c r="E5" s="11" t="n">
+        <v>3074074</v>
+      </c>
+      <c r="F5" s="11" t="n">
+        <v>731413</v>
+      </c>
+      <c r="G5" s="11" t="n">
+        <v>1967</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>Universal · 6-mo postnatal</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="n">
+        <v>6573014</v>
+      </c>
+      <c r="D6" s="11" t="n">
+        <v>2070950</v>
+      </c>
+      <c r="E6" s="11" t="n">
+        <v>4502064</v>
+      </c>
+      <c r="F6" s="11" t="n">
+        <v>1135057</v>
+      </c>
+      <c r="G6" s="11" t="n">
+        <v>2881</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>Universal · 6-mo postnatal</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>Honolulu</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="n">
+        <v>35552651</v>
+      </c>
+      <c r="D7" s="11" t="n">
+        <v>11201520</v>
+      </c>
+      <c r="E7" s="11" t="n">
+        <v>24351131</v>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>2020865</v>
+      </c>
+      <c r="G7" s="11" t="n">
+        <v>15585</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>Universal · 6-mo postnatal</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>Kauai</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="n">
+        <v>1887751</v>
+      </c>
+      <c r="D8" s="11" t="n">
+        <v>594771</v>
+      </c>
+      <c r="E8" s="11" t="n">
+        <v>1292980</v>
+      </c>
+      <c r="F8" s="11" t="n">
+        <v>445089</v>
+      </c>
+      <c r="G8" s="11" t="n">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>Universal · 6-mo postnatal</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>Maui</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="n">
+        <v>5788346</v>
+      </c>
+      <c r="D9" s="11" t="n">
+        <v>1823725</v>
+      </c>
+      <c r="E9" s="11" t="n">
+        <v>3964621</v>
+      </c>
+      <c r="F9" s="11" t="n">
+        <v>794091</v>
+      </c>
+      <c r="G9" s="11" t="n">
+        <v>2537</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>Universal · 12-mo postnatal</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="n">
+        <v>11075078</v>
+      </c>
+      <c r="D10" s="11" t="n">
+        <v>2070950</v>
+      </c>
+      <c r="E10" s="11" t="n">
+        <v>9004129</v>
+      </c>
+      <c r="F10" s="11" t="n">
+        <v>1912494</v>
+      </c>
+      <c r="G10" s="11" t="n">
+        <v>2881</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>Universal · 12-mo postnatal</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Honolulu</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="n">
+        <v>59903782</v>
+      </c>
+      <c r="D11" s="11" t="n">
+        <v>11201520</v>
+      </c>
+      <c r="E11" s="11" t="n">
+        <v>48702262</v>
+      </c>
+      <c r="F11" s="11" t="n">
+        <v>3405019</v>
+      </c>
+      <c r="G11" s="11" t="n">
+        <v>15585</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>Universal · 12-mo postnatal</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>Kauai</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="n">
+        <v>3180732</v>
+      </c>
+      <c r="D12" s="11" t="n">
+        <v>594771</v>
+      </c>
+      <c r="E12" s="11" t="n">
+        <v>2585961</v>
+      </c>
+      <c r="F12" s="11" t="n">
+        <v>749945</v>
+      </c>
+      <c r="G12" s="11" t="n">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>Universal · 12-mo postnatal</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>Maui</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="n">
+        <v>9752967</v>
+      </c>
+      <c r="D13" s="11" t="n">
+        <v>1823725</v>
+      </c>
+      <c r="E13" s="11" t="n">
+        <v>7929241</v>
+      </c>
+      <c r="F13" s="11" t="n">
+        <v>1337990</v>
+      </c>
+      <c r="G13" s="11" t="n">
+        <v>2537</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1302,7 +1941,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>15,419 -&gt; 13,632</t>
+          <t>14,176 -&gt; 13,632</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1416,7 +2055,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/reports/rxkids_2028/rxkids_2028_cost_and_impact.xlsx
+++ b/reports/rxkids_2028/rxkids_2028_cost_and_impact.xlsx
@@ -778,7 +778,7 @@
         </is>
       </c>
       <c r="B33" s="6" t="n">
-        <v>7326.023534804361</v>
+        <v>7326.02353480436</v>
       </c>
     </row>
     <row r="34">
@@ -871,7 +871,7 @@
         <v>15315</v>
       </c>
       <c r="C2" s="11" t="n">
-        <v>107149</v>
+        <v>107150</v>
       </c>
       <c r="D2" s="11" t="n">
         <v>2230</v>
@@ -896,7 +896,7 @@
         <v>52619</v>
       </c>
       <c r="C3" s="11" t="n">
-        <v>107150</v>
+        <v>107149</v>
       </c>
       <c r="D3" s="11" t="n">
         <v>4377</v>

--- a/reports/rxkids_2028/rxkids_2028_cost_and_impact.xlsx
+++ b/reports/rxkids_2028/rxkids_2028_cost_and_impact.xlsx
@@ -528,7 +528,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>32087983.0824431</v>
+        <v>31317051.79548059</v>
       </c>
     </row>
     <row r="6">
@@ -538,7 +538,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>10109912.47803002</v>
+        <v>9867016.319124021</v>
       </c>
     </row>
     <row r="7">
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>21978070.60441308</v>
+        <v>21450035.47635657</v>
       </c>
     </row>
     <row r="8">
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>2567038.646595448</v>
+        <v>2505364.143638447</v>
       </c>
     </row>
     <row r="9">
@@ -568,7 +568,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>34655021.72903854</v>
+        <v>33822415.93911904</v>
       </c>
     </row>
     <row r="10">
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>28633407.51224043</v>
+        <v>23501385.31149371</v>
       </c>
     </row>
     <row r="11">
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>35542558.65264577</v>
+        <v>39132718.27946748</v>
       </c>
     </row>
     <row r="12">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>2100045.93933293</v>
+        <v>4751165.03585829</v>
       </c>
     </row>
     <row r="13">
@@ -608,7 +608,7 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>19252789.84946586</v>
+        <v>18790231.07728836</v>
       </c>
     </row>
     <row r="14">
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>40912788.93207619</v>
+        <v>39929836.87355655</v>
       </c>
     </row>
     <row r="15">
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>21978070.60441308</v>
+        <v>21450035.47635657</v>
       </c>
     </row>
     <row r="18">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>54066053.68685618</v>
+        <v>52767087.27183717</v>
       </c>
     </row>
     <row r="19">
@@ -668,7 +668,7 @@
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>13310977.76143204</v>
+        <v>12991174.26396744</v>
       </c>
     </row>
     <row r="22">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>5476202.59226626</v>
+        <v>5344633.839525511</v>
       </c>
     </row>
     <row r="23">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>7834775.169165776</v>
+        <v>7646540.424441926</v>
       </c>
     </row>
     <row r="24">
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>4070013.074891313</v>
+        <v>3972228.791917885</v>
       </c>
     </row>
     <row r="25">
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>20824221.89768139</v>
+        <v>20323908.61384785</v>
       </c>
     </row>
     <row r="27">
@@ -728,7 +728,7 @@
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>8873985.174288023</v>
+        <v>8660782.842644958</v>
       </c>
     </row>
     <row r="28">
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>8158</v>
+        <v>7340</v>
       </c>
     </row>
     <row r="31">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>14065.96518682437</v>
+        <v>13728.02270486821</v>
       </c>
     </row>
     <row r="32">
@@ -768,7 +768,7 @@
         </is>
       </c>
       <c r="B32" s="6" t="n">
-        <v>6739.941652020011</v>
+        <v>6578.010879416015</v>
       </c>
     </row>
     <row r="33">
@@ -778,7 +778,7 @@
         </is>
       </c>
       <c r="B33" s="6" t="n">
-        <v>7326.02353480436</v>
+        <v>7150.011825452191</v>
       </c>
     </row>
     <row r="34">
@@ -868,22 +868,22 @@
         </is>
       </c>
       <c r="B2" s="11" t="n">
-        <v>15315</v>
+        <v>17182</v>
       </c>
       <c r="C2" s="11" t="n">
-        <v>107150</v>
+        <v>110267</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>2230</v>
+        <v>722</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>5087073</v>
+        <v>1647671</v>
       </c>
       <c r="F2" s="11" t="n">
         <v>2281</v>
       </c>
       <c r="G2" s="12" t="n">
-        <v>15.9</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="3">
@@ -893,22 +893,22 @@
         </is>
       </c>
       <c r="B3" s="11" t="n">
-        <v>52619</v>
+        <v>57026</v>
       </c>
       <c r="C3" s="11" t="n">
-        <v>107149</v>
+        <v>110263</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>4377</v>
+        <v>4481</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>9984613</v>
+        <v>10221201</v>
       </c>
       <c r="F3" s="11" t="n">
         <v>2281</v>
       </c>
       <c r="G3" s="12" t="n">
-        <v>31.1</v>
+        <v>32.6</v>
       </c>
     </row>
     <row r="4">
@@ -918,22 +918,22 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>92200</v>
+        <v>96722</v>
       </c>
       <c r="C4" s="11" t="n">
-        <v>107159</v>
+        <v>110317</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>3745</v>
+        <v>4313</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>8544160</v>
+        <v>9837998</v>
       </c>
       <c r="F4" s="11" t="n">
         <v>2281</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>26.6</v>
+        <v>31.4</v>
       </c>
     </row>
     <row r="5">
@@ -943,22 +943,22 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>146436</v>
+        <v>154809</v>
       </c>
       <c r="C5" s="11" t="n">
-        <v>107149</v>
+        <v>110231</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>2690</v>
+        <v>2594</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>6137087</v>
+        <v>5916636</v>
       </c>
       <c r="F5" s="11" t="n">
         <v>2281</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>19.1</v>
+        <v>18.9</v>
       </c>
     </row>
     <row r="6">
@@ -968,22 +968,22 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>307932</v>
+        <v>334087</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>107157</v>
+        <v>110343</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>1024</v>
+        <v>1619</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>2335050</v>
+        <v>3693545</v>
       </c>
       <c r="F6" s="11" t="n">
         <v>2281</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>7.3</v>
+        <v>11.8</v>
       </c>
     </row>
   </sheetData>
@@ -1047,19 +1047,19 @@
         </is>
       </c>
       <c r="B2" s="11" t="n">
-        <v>4609449</v>
+        <v>4533949</v>
       </c>
       <c r="C2" s="11" t="n">
-        <v>1452292</v>
+        <v>1428505</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>3157157</v>
+        <v>3105445</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>907555</v>
+        <v>1535552</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>2021</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="3">
@@ -1069,19 +1069,19 @@
         </is>
       </c>
       <c r="B3" s="11" t="n">
-        <v>21932790</v>
+        <v>22915140</v>
       </c>
       <c r="C3" s="11" t="n">
-        <v>6910331</v>
+        <v>7219839</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>15022459</v>
+        <v>15695301</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>1594676</v>
+        <v>4279553</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>9614</v>
+        <v>10045</v>
       </c>
     </row>
     <row r="4">
@@ -1091,19 +1091,19 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>1057596</v>
+        <v>2371759</v>
       </c>
       <c r="C4" s="11" t="n">
-        <v>333215</v>
+        <v>747267</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>724381</v>
+        <v>1624493</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>271196</v>
+        <v>1367410</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>464</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="5">
@@ -1113,19 +1113,19 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>4488148</v>
+        <v>1496203</v>
       </c>
       <c r="C5" s="11" t="n">
-        <v>1414074</v>
+        <v>471407</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>3074074</v>
+        <v>1024797</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>731413</v>
+        <v>739313</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>1967</v>
+        <v>656</v>
       </c>
     </row>
   </sheetData>
@@ -1255,34 +1255,34 @@
         <v>4500</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>32087983</v>
+        <v>31317052</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>10109912</v>
+        <v>9867016</v>
       </c>
       <c r="G3" s="11" t="n">
-        <v>21978071</v>
+        <v>21450035</v>
       </c>
       <c r="H3" s="11" t="n">
-        <v>2567039</v>
+        <v>2505364</v>
       </c>
       <c r="I3" s="11" t="n">
-        <v>34655022</v>
+        <v>33822416</v>
       </c>
       <c r="J3" s="11" t="n">
-        <v>19252790</v>
+        <v>18790231</v>
       </c>
       <c r="K3" s="11" t="n">
-        <v>40912789</v>
+        <v>39929837</v>
       </c>
       <c r="L3" s="11" t="n">
-        <v>14066</v>
+        <v>13728</v>
       </c>
       <c r="M3" s="11" t="n">
         <v>2281</v>
       </c>
       <c r="N3" s="11" t="n">
-        <v>13310978</v>
+        <v>12991174</v>
       </c>
     </row>
     <row r="4">
@@ -1303,34 +1303,34 @@
         <v>4500</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>49801763</v>
+        <v>53327865</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>15690966</v>
+        <v>16801930</v>
       </c>
       <c r="G4" s="11" t="n">
-        <v>34110796</v>
+        <v>36525935</v>
       </c>
       <c r="H4" s="11" t="n">
-        <v>3984141</v>
+        <v>4266229</v>
       </c>
       <c r="I4" s="11" t="n">
-        <v>53785904</v>
+        <v>57594094</v>
       </c>
       <c r="J4" s="11" t="n">
-        <v>29881058</v>
+        <v>31996719</v>
       </c>
       <c r="K4" s="11" t="n">
-        <v>63498195</v>
+        <v>67994042</v>
       </c>
       <c r="L4" s="11" t="n">
-        <v>21831</v>
+        <v>23377</v>
       </c>
       <c r="M4" s="11" t="n">
         <v>2281</v>
       </c>
       <c r="N4" s="11" t="n">
-        <v>20659141</v>
+        <v>22121865</v>
       </c>
     </row>
     <row r="5">
@@ -1351,34 +1351,34 @@
         <v>7500</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>83912559</v>
+        <v>89853799</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>15690966</v>
+        <v>16801930</v>
       </c>
       <c r="G5" s="11" t="n">
-        <v>68221593</v>
+        <v>73051869</v>
       </c>
       <c r="H5" s="11" t="n">
-        <v>6713005</v>
+        <v>7188304</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>90625564</v>
+        <v>97042103</v>
       </c>
       <c r="J5" s="11" t="n">
-        <v>50347535</v>
+        <v>53912280</v>
       </c>
       <c r="K5" s="11" t="n">
-        <v>106989460</v>
+        <v>114564609</v>
       </c>
       <c r="L5" s="11" t="n">
-        <v>21831</v>
+        <v>23377</v>
       </c>
       <c r="M5" s="11" t="n">
         <v>3844</v>
       </c>
       <c r="N5" s="11" t="n">
-        <v>22870026</v>
+        <v>24489286</v>
       </c>
     </row>
   </sheetData>
@@ -1453,19 +1453,19 @@
         </is>
       </c>
       <c r="C2" s="11" t="n">
-        <v>4609449</v>
+        <v>4533949</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>1452292</v>
+        <v>1428505</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>3157157</v>
+        <v>3105445</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>907555</v>
+        <v>1535552</v>
       </c>
       <c r="G2" s="11" t="n">
-        <v>2021</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="3">
@@ -1480,19 +1480,19 @@
         </is>
       </c>
       <c r="C3" s="11" t="n">
-        <v>21932790</v>
+        <v>22915140</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>6910331</v>
+        <v>7219839</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>15022459</v>
+        <v>15695301</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>1594676</v>
+        <v>4279553</v>
       </c>
       <c r="G3" s="11" t="n">
-        <v>9614</v>
+        <v>10045</v>
       </c>
     </row>
     <row r="4">
@@ -1507,19 +1507,19 @@
         </is>
       </c>
       <c r="C4" s="11" t="n">
-        <v>1057596</v>
+        <v>2371759</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>333215</v>
+        <v>747267</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>724381</v>
+        <v>1624493</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>271196</v>
+        <v>1367410</v>
       </c>
       <c r="G4" s="11" t="n">
-        <v>464</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="5">
@@ -1534,19 +1534,19 @@
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>4488148</v>
+        <v>1496203</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>1414074</v>
+        <v>471407</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>3074074</v>
+        <v>1024797</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>731413</v>
+        <v>739313</v>
       </c>
       <c r="G5" s="11" t="n">
-        <v>1967</v>
+        <v>656</v>
       </c>
     </row>
     <row r="6">
@@ -1561,19 +1561,19 @@
         </is>
       </c>
       <c r="C6" s="11" t="n">
-        <v>6573014</v>
+        <v>4533949</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>2070950</v>
+        <v>1428505</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>4502064</v>
+        <v>3105445</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>1135057</v>
+        <v>1535552</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>2881</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="7">
@@ -1588,19 +1588,19 @@
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>35552651</v>
+        <v>41227929</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>11201520</v>
+        <v>12989622</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>24351131</v>
+        <v>28238308</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>2020865</v>
+        <v>6385174</v>
       </c>
       <c r="G7" s="11" t="n">
-        <v>15585</v>
+        <v>18073</v>
       </c>
     </row>
     <row r="8">
@@ -1615,19 +1615,19 @@
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>1887751</v>
+        <v>2371759</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>594771</v>
+        <v>747267</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>1292980</v>
+        <v>1624493</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>445089</v>
+        <v>1367410</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>828</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="9">
@@ -1642,19 +1642,19 @@
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>5788346</v>
+        <v>5194227</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>1823725</v>
+        <v>1636537</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>3964621</v>
+        <v>3557690</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>794091</v>
+        <v>2613546</v>
       </c>
       <c r="G9" s="11" t="n">
-        <v>2537</v>
+        <v>2277</v>
       </c>
     </row>
     <row r="10">
@@ -1669,19 +1669,19 @@
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>11075078</v>
+        <v>7639394</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>2070950</v>
+        <v>1428505</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>9004129</v>
+        <v>6210890</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>1912494</v>
+        <v>2587300</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>2881</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="11">
@@ -1696,19 +1696,19 @@
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>59903782</v>
+        <v>69466237</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>11201520</v>
+        <v>12989622</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>48702262</v>
+        <v>56476615</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>3405019</v>
+        <v>10758581</v>
       </c>
       <c r="G11" s="11" t="n">
-        <v>15585</v>
+        <v>18073</v>
       </c>
     </row>
     <row r="12">
@@ -1723,19 +1723,19 @@
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>3180732</v>
+        <v>3996252</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>594771</v>
+        <v>747267</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>2585961</v>
+        <v>3248985</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>749945</v>
+        <v>2303993</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>828</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="13">
@@ -1750,19 +1750,19 @@
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>9752967</v>
+        <v>8751916</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>1823725</v>
+        <v>1636537</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>7929241</v>
+        <v>7115379</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>1337990</v>
+        <v>4403646</v>
       </c>
       <c r="G13" s="11" t="n">
-        <v>2537</v>
+        <v>2277</v>
       </c>
     </row>
   </sheetData>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>14,176 -&gt; 13,632</t>
+          <t>12,755 -&gt; 14,127</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2080,7 +2080,7 @@
     <row r="3">
       <c r="A3" s="14" t="inlineStr">
         <is>
-          <t>Both arms are driven by OBSERVED births — the count of age-0 dependents in each PUMS tax unit (an infant &lt;1yr ≈ a birth in the last 12 months, the annual flow). The weighted count is calibrated to CDC NVSR resident births (by-residence basis, 2022=15,535), then projected to 2028 with the repo's damped-trend ensemble (point 13,632, 90% PI [10,502, 16,761]). Each birth draws one prenatal + one postnatal payment. This replaces the legacy num_dependents × rate proxy, which multiplied an all-dependents count (incl. older children, students, adult dependents) by a children-only-calibrated rate and overstated total births ~1.7×. Cost = the take-up-adjusted benefit weighted by the household (WGTP) weight, summed to SPM-unit grain. Per-unit amounts are expectations, not literal payments.</t>
+          <t>Both arms are driven by OBSERVED births — the count of age-0 dependents in each PUMS tax unit (an infant &lt;1yr ≈ a birth in the last 12 months, the annual flow). The weighted count is calibrated to CDC NVSR resident births (by-residence basis, 2022=15,535), then projected to 2028 with the repo's damped-trend ensemble (point 14,127, 90% PI [13,071, 15,183]). NVSR finals run through 2024; later years are nowcast from Hawaiʻi DOH preliminary births (snapshot 2026-07-06) converted occurrence→residence at ÷1.0055 (sd 0.0050, carried into their MOEs): 2025≈14,499; 2026≈14,374 (annualised from 5mo). Each birth draws one prenatal + one postnatal payment. This replaces the legacy num_dependents × rate proxy, which multiplied an all-dependents count (incl. older children, students, adult dependents) by a children-only-calibrated rate and overstated total births ~1.7×. Cost = the take-up-adjusted benefit weighted by the household (WGTP) weight, summed to SPM-unit grain. Per-unit amounts are expectations, not literal payments.</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>Caveats: 2026-2028 FPL is CPI-projected off the 2025 HHS table. The birth cohort is projected with the ensemble (vital-statistics counts, not survey estimates); update HI_BIRTHS_BY_YEAR as new NVSR final-data releases land.</t>
+          <t>Caveats: 2026-2028 FPL is CPI-projected off the 2025 HHS table. The birth cohort is projected with the ensemble (vital-statistics counts, not survey estimates); update HI_BIRTHS_BY_YEAR as new NVSR final-data releases land, and re-pull HI_DOH_BIRTHS_MONTHLY (bump DOH_SNAPSHOT) for the nowcast years. The occurrence-&gt;residence factor is calibrated on the post-2020 travel regime; a recovery toward the pre-COVID ~1.10 would make the nowcasts high.</t>
         </is>
       </c>
     </row>

--- a/reports/rxkids_2028/rxkids_2028_cost_and_impact.xlsx
+++ b/reports/rxkids_2028/rxkids_2028_cost_and_impact.xlsx
@@ -528,7 +528,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>31317051.79548059</v>
+        <v>31961813.23414758</v>
       </c>
     </row>
     <row r="6">
@@ -538,7 +538,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>9867016.319124021</v>
+        <v>10070160.33404649</v>
       </c>
     </row>
     <row r="7">
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>21450035.47635657</v>
+        <v>21891652.90010108</v>
       </c>
     </row>
     <row r="8">
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>2505364.143638447</v>
+        <v>2556945.058731806</v>
       </c>
     </row>
     <row r="9">
@@ -568,7 +568,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>33822415.93911904</v>
+        <v>34518758.29287939</v>
       </c>
     </row>
     <row r="10">
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>23501385.31149371</v>
+        <v>24247070.60404436</v>
       </c>
     </row>
     <row r="11">
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>39132718.27946748</v>
+        <v>39676555.86425079</v>
       </c>
     </row>
     <row r="12">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>4751165.03585829</v>
+        <v>4689813.148998917</v>
       </c>
     </row>
     <row r="13">
@@ -608,7 +608,7 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>18790231.07728836</v>
+        <v>19177087.94048855</v>
       </c>
     </row>
     <row r="14">
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>39929836.87355655</v>
+        <v>40751919.97500761</v>
       </c>
     </row>
     <row r="15">
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>21450035.47635657</v>
+        <v>21891652.90010108</v>
       </c>
     </row>
     <row r="18">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>52767087.27183717</v>
+        <v>53853466.13424866</v>
       </c>
     </row>
     <row r="19">
@@ -668,7 +668,7 @@
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>12991174.26396744</v>
+        <v>13258639.03884825</v>
       </c>
     </row>
     <row r="22">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>5344633.839525511</v>
+        <v>5454670.180941851</v>
       </c>
     </row>
     <row r="23">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>7646540.424441926</v>
+        <v>7803968.857906403</v>
       </c>
     </row>
     <row r="24">
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>3972228.791917885</v>
+        <v>4054009.796315014</v>
       </c>
     </row>
     <row r="25">
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>20323908.61384785</v>
+        <v>20742341.12284577</v>
       </c>
     </row>
     <row r="27">
@@ -728,7 +728,7 @@
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>8660782.842644958</v>
+        <v>8839092.692565504</v>
       </c>
     </row>
     <row r="28">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>13728.02270486821</v>
+        <v>14010.65785606469</v>
       </c>
     </row>
     <row r="32">
@@ -768,7 +768,7 @@
         </is>
       </c>
       <c r="B32" s="6" t="n">
-        <v>6578.010879416015</v>
+        <v>6713.440222697664</v>
       </c>
     </row>
     <row r="33">
@@ -778,7 +778,7 @@
         </is>
       </c>
       <c r="B33" s="6" t="n">
-        <v>7150.011825452191</v>
+        <v>7297.217633367027</v>
       </c>
     </row>
     <row r="34">
@@ -874,16 +874,16 @@
         <v>110267</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>722</v>
+        <v>772</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>1647671</v>
+        <v>1760415</v>
       </c>
       <c r="F2" s="11" t="n">
         <v>2281</v>
       </c>
       <c r="G2" s="12" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="3">
@@ -893,22 +893,22 @@
         </is>
       </c>
       <c r="B3" s="11" t="n">
-        <v>57026</v>
+        <v>57024</v>
       </c>
       <c r="C3" s="11" t="n">
         <v>110263</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>4481</v>
+        <v>4679</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>10221201</v>
+        <v>10673739</v>
       </c>
       <c r="F3" s="11" t="n">
         <v>2281</v>
       </c>
       <c r="G3" s="12" t="n">
-        <v>32.6</v>
+        <v>33.4</v>
       </c>
     </row>
     <row r="4">
@@ -924,16 +924,16 @@
         <v>110317</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>4313</v>
+        <v>4200</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>9837998</v>
+        <v>9580498</v>
       </c>
       <c r="F4" s="11" t="n">
         <v>2281</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>31.4</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5">
@@ -949,16 +949,16 @@
         <v>110231</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>2594</v>
+        <v>2739</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>5916636</v>
+        <v>6247330</v>
       </c>
       <c r="F5" s="11" t="n">
         <v>2281</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>18.9</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="6">
@@ -974,16 +974,16 @@
         <v>110343</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>3693545</v>
+        <v>3699833</v>
       </c>
       <c r="F6" s="11" t="n">
         <v>2281</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>11.8</v>
+        <v>11.6</v>
       </c>
     </row>
   </sheetData>
@@ -1047,19 +1047,19 @@
         </is>
       </c>
       <c r="B2" s="11" t="n">
-        <v>4533949</v>
+        <v>6382030</v>
       </c>
       <c r="C2" s="11" t="n">
-        <v>1428505</v>
+        <v>2010777</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>3105445</v>
+        <v>4371253</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>1535552</v>
+        <v>2161457</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>1987</v>
+        <v>2798</v>
       </c>
     </row>
     <row r="3">
@@ -1069,19 +1069,19 @@
         </is>
       </c>
       <c r="B3" s="11" t="n">
-        <v>22915140</v>
+        <v>21904984</v>
       </c>
       <c r="C3" s="11" t="n">
-        <v>7219839</v>
+        <v>6901570</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>15695301</v>
+        <v>15003414</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>4279553</v>
+        <v>4090900</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>10045</v>
+        <v>9602</v>
       </c>
     </row>
     <row r="4">
@@ -1091,19 +1091,19 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>2371759</v>
+        <v>2171819</v>
       </c>
       <c r="C4" s="11" t="n">
-        <v>747267</v>
+        <v>684272</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>1624493</v>
+        <v>1487547</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>1367410</v>
+        <v>1252137</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>1040</v>
+        <v>952</v>
       </c>
     </row>
     <row r="5">
@@ -1113,19 +1113,19 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>1496203</v>
+        <v>1502980</v>
       </c>
       <c r="C5" s="11" t="n">
-        <v>471407</v>
+        <v>473542</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>1024797</v>
+        <v>1029439</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>739313</v>
+        <v>740584</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>656</v>
+        <v>659</v>
       </c>
     </row>
   </sheetData>
@@ -1255,34 +1255,34 @@
         <v>4500</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>31317052</v>
+        <v>31961813</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>9867016</v>
+        <v>10070160</v>
       </c>
       <c r="G3" s="11" t="n">
-        <v>21450035</v>
+        <v>21891653</v>
       </c>
       <c r="H3" s="11" t="n">
-        <v>2505364</v>
+        <v>2556945</v>
       </c>
       <c r="I3" s="11" t="n">
-        <v>33822416</v>
+        <v>34518758</v>
       </c>
       <c r="J3" s="11" t="n">
-        <v>18790231</v>
+        <v>19177088</v>
       </c>
       <c r="K3" s="11" t="n">
-        <v>39929837</v>
+        <v>40751920</v>
       </c>
       <c r="L3" s="11" t="n">
-        <v>13728</v>
+        <v>14011</v>
       </c>
       <c r="M3" s="11" t="n">
         <v>2281</v>
       </c>
       <c r="N3" s="11" t="n">
-        <v>12991174</v>
+        <v>13258639</v>
       </c>
     </row>
     <row r="4">
@@ -1303,34 +1303,34 @@
         <v>4500</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>53327865</v>
+        <v>53259558</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>16801930</v>
+        <v>16780409</v>
       </c>
       <c r="G4" s="11" t="n">
-        <v>36525935</v>
+        <v>36479149</v>
       </c>
       <c r="H4" s="11" t="n">
-        <v>4266229</v>
+        <v>4260765</v>
       </c>
       <c r="I4" s="11" t="n">
-        <v>57594094</v>
+        <v>57520322</v>
       </c>
       <c r="J4" s="11" t="n">
-        <v>31996719</v>
+        <v>31955735</v>
       </c>
       <c r="K4" s="11" t="n">
-        <v>67994042</v>
+        <v>67906949</v>
       </c>
       <c r="L4" s="11" t="n">
-        <v>23377</v>
+        <v>23347</v>
       </c>
       <c r="M4" s="11" t="n">
         <v>2281</v>
       </c>
       <c r="N4" s="11" t="n">
-        <v>22121865</v>
+        <v>22093529</v>
       </c>
     </row>
     <row r="5">
@@ -1351,34 +1351,34 @@
         <v>7500</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>89853799</v>
+        <v>89738707</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>16801930</v>
+        <v>16780409</v>
       </c>
       <c r="G5" s="11" t="n">
-        <v>73051869</v>
+        <v>72958298</v>
       </c>
       <c r="H5" s="11" t="n">
-        <v>7188304</v>
+        <v>7179097</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>97042103</v>
+        <v>96917803</v>
       </c>
       <c r="J5" s="11" t="n">
-        <v>53912280</v>
+        <v>53843224</v>
       </c>
       <c r="K5" s="11" t="n">
-        <v>114564609</v>
+        <v>114417864</v>
       </c>
       <c r="L5" s="11" t="n">
-        <v>23377</v>
+        <v>23347</v>
       </c>
       <c r="M5" s="11" t="n">
         <v>3844</v>
       </c>
       <c r="N5" s="11" t="n">
-        <v>24489286</v>
+        <v>24457918</v>
       </c>
     </row>
   </sheetData>
@@ -1453,19 +1453,19 @@
         </is>
       </c>
       <c r="C2" s="11" t="n">
-        <v>4533949</v>
+        <v>6382030</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>1428505</v>
+        <v>2010777</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>3105445</v>
+        <v>4371253</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>1535552</v>
+        <v>2161457</v>
       </c>
       <c r="G2" s="11" t="n">
-        <v>1987</v>
+        <v>2798</v>
       </c>
     </row>
     <row r="3">
@@ -1480,19 +1480,19 @@
         </is>
       </c>
       <c r="C3" s="11" t="n">
-        <v>22915140</v>
+        <v>21904984</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>7219839</v>
+        <v>6901570</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>15695301</v>
+        <v>15003414</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>4279553</v>
+        <v>4090900</v>
       </c>
       <c r="G3" s="11" t="n">
-        <v>10045</v>
+        <v>9602</v>
       </c>
     </row>
     <row r="4">
@@ -1507,19 +1507,19 @@
         </is>
       </c>
       <c r="C4" s="11" t="n">
-        <v>2371759</v>
+        <v>2171819</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>747267</v>
+        <v>684272</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>1624493</v>
+        <v>1487547</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>1367410</v>
+        <v>1252137</v>
       </c>
       <c r="G4" s="11" t="n">
-        <v>1040</v>
+        <v>952</v>
       </c>
     </row>
     <row r="5">
@@ -1534,19 +1534,19 @@
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>1496203</v>
+        <v>1502980</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>471407</v>
+        <v>473542</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>1024797</v>
+        <v>1029439</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>739313</v>
+        <v>740584</v>
       </c>
       <c r="G5" s="11" t="n">
-        <v>656</v>
+        <v>659</v>
       </c>
     </row>
     <row r="6">
@@ -1561,19 +1561,19 @@
         </is>
       </c>
       <c r="C6" s="11" t="n">
-        <v>4533949</v>
+        <v>6382030</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>1428505</v>
+        <v>2010777</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>3105445</v>
+        <v>4371253</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>1535552</v>
+        <v>2161457</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>1987</v>
+        <v>2798</v>
       </c>
     </row>
     <row r="7">
@@ -1588,19 +1588,19 @@
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>41227929</v>
+        <v>39410501</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>12989622</v>
+        <v>12417007</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>28238308</v>
+        <v>26993494</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>6385174</v>
+        <v>6103700</v>
       </c>
       <c r="G7" s="11" t="n">
-        <v>18073</v>
+        <v>17276</v>
       </c>
     </row>
     <row r="8">
@@ -1615,19 +1615,19 @@
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>2371759</v>
+        <v>2171819</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>747267</v>
+        <v>684272</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>1624493</v>
+        <v>1487547</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>1367410</v>
+        <v>1252137</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>1040</v>
+        <v>952</v>
       </c>
     </row>
     <row r="9">
@@ -1642,19 +1642,19 @@
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>5194227</v>
+        <v>5295208</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>1636537</v>
+        <v>1668353</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>3557690</v>
+        <v>3626855</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>2613546</v>
+        <v>2673560</v>
       </c>
       <c r="G9" s="11" t="n">
-        <v>2277</v>
+        <v>2321</v>
       </c>
     </row>
     <row r="10">
@@ -1669,19 +1669,19 @@
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>7639394</v>
+        <v>10753283</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>1428505</v>
+        <v>2010777</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>6210890</v>
+        <v>8742507</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>2587300</v>
+        <v>3641907</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>1987</v>
+        <v>2798</v>
       </c>
     </row>
     <row r="11">
@@ -1696,19 +1696,19 @@
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>69466237</v>
+        <v>66403995</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>12989622</v>
+        <v>12417007</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>56476615</v>
+        <v>53986988</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>10758581</v>
+        <v>10284316</v>
       </c>
       <c r="G11" s="11" t="n">
-        <v>18073</v>
+        <v>17276</v>
       </c>
     </row>
     <row r="12">
@@ -1723,19 +1723,19 @@
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>3996252</v>
+        <v>3659366</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>747267</v>
+        <v>684272</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>3248985</v>
+        <v>2975094</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>2303993</v>
+        <v>2109765</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>1040</v>
+        <v>952</v>
       </c>
     </row>
     <row r="13">
@@ -1750,19 +1750,19 @@
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>8751916</v>
+        <v>8922063</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>1636537</v>
+        <v>1668353</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>7115379</v>
+        <v>7253710</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>4403646</v>
+        <v>4504766</v>
       </c>
       <c r="G13" s="11" t="n">
-        <v>2277</v>
+        <v>2321</v>
       </c>
     </row>
   </sheetData>
@@ -2080,7 +2080,7 @@
     <row r="3">
       <c r="A3" s="14" t="inlineStr">
         <is>
-          <t>Both arms are driven by OBSERVED births — the count of age-0 dependents in each PUMS tax unit (an infant &lt;1yr ≈ a birth in the last 12 months, the annual flow). The weighted count is calibrated to CDC NVSR resident births (by-residence basis, 2022=15,535), then projected to 2028 with the repo's damped-trend ensemble (point 14,127, 90% PI [13,071, 15,183]). NVSR finals run through 2024; later years are nowcast from Hawaiʻi DOH preliminary births (snapshot 2026-07-06) converted occurrence→residence at ÷1.0055 (sd 0.0050, carried into their MOEs): 2025≈14,499; 2026≈14,374 (annualised from 5mo). Each birth draws one prenatal + one postnatal payment. This replaces the legacy num_dependents × rate proxy, which multiplied an all-dependents count (incl. older children, students, adult dependents) by a children-only-calibrated rate and overstated total births ~1.7×. Cost = the take-up-adjusted benefit weighted by the household (WGTP) weight, summed to SPM-unit grain. Per-unit amounts are expectations, not literal payments.</t>
+          <t>Both arms are driven by OBSERVED births — the count of age-0 dependents in each PUMS tax unit (an infant &lt;1yr ≈ a birth in the last 12 months, the annual flow). The weighted count is calibrated to CDC NVSR resident births (by-residence basis, 2022=15,535), then projected to 2028 with the repo's damped-trend ensemble (point 14,127, 90% PI [13,071, 15,183]). NVSR finals run through 2024; later years are nowcast from Hawaiʻi DOH preliminary births (snapshot 2026-07-06) converted occurrence→residence at ÷1.0055 (sd 0.0050, carried into their MOEs): 2025≈14,499; 2026≈14,374 (annualised from 5mo). Each birth draws one prenatal + one postnatal payment. This replaces the legacy num_dependents × rate proxy, which multiplied an all-dependents count (incl. older children, students, adult dependents) by a children-only-calibrated rate and overstated total births ~1.7×. County split: recalibrated to Hawaiʻi DOH's aggregate county vital-statistics shares (2018-2025), not raw PUMS county shares — PUMS's own county allocation is small-sample-noisy (Hawaii County carries only ~11 sampled infants) and Maui/Kauai are not independently sampled at all (one combined PUMA, split by a demographic-heuristic imputer, not survey evidence). Per-county factor vs the raw PUMS-implied count: Honolulu×0.96; Hawaii×1.41; Maui×1.03; Kauai×0.92. The state BIRTH total is unchanged (redistribution only), but the state COST total is NOT — eligibility is unit-specific and correlated with county, so this also corrects the eligible share (measured +2.1% on cost/recipients on the real frame; eligible_families itself is unchanged). --no-doh-county-shares restores raw PUMS shares. Cost = the take-up-adjusted benefit weighted by the household (WGTP) weight, summed to SPM-unit grain. Per-unit amounts are expectations, not literal payments.</t>
         </is>
       </c>
     </row>

--- a/reports/rxkids_2028/rxkids_2028_cost_and_impact.xlsx
+++ b/reports/rxkids_2028/rxkids_2028_cost_and_impact.xlsx
@@ -528,7 +528,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>31961813.23414758</v>
+        <v>32058217.42200988</v>
       </c>
     </row>
     <row r="6">
@@ -538,7 +538,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>10070160.33404649</v>
+        <v>10100534.25624969</v>
       </c>
     </row>
     <row r="7">
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>21891652.90010108</v>
+        <v>21957683.16576019</v>
       </c>
     </row>
     <row r="8">
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>2556945.058731806</v>
+        <v>2564657.39376079</v>
       </c>
     </row>
     <row r="9">
@@ -568,7 +568,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>34518758.29287939</v>
+        <v>34622874.81577067</v>
       </c>
     </row>
     <row r="10">
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>24247070.60404436</v>
+        <v>24364840.04645819</v>
       </c>
     </row>
     <row r="11">
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>39676555.86425079</v>
+        <v>39751594.79756156</v>
       </c>
     </row>
     <row r="12">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>4689813.148998917</v>
+        <v>4676825.152311054</v>
       </c>
     </row>
     <row r="13">
@@ -608,7 +608,7 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>19177087.94048855</v>
+        <v>19234930.45320593</v>
       </c>
     </row>
     <row r="14">
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>40751919.97500761</v>
+        <v>40874837.14870609</v>
       </c>
     </row>
     <row r="15">
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>21891652.90010108</v>
+        <v>21957683.1657602</v>
       </c>
     </row>
     <row r="18">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>53853466.13424866</v>
+        <v>54015900.58777007</v>
       </c>
     </row>
     <row r="19">
@@ -668,7 +668,7 @@
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>13258639.03884825</v>
+        <v>13298630.14696643</v>
       </c>
     </row>
     <row r="22">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>5454670.180941851</v>
+        <v>5471122.722135249</v>
       </c>
     </row>
     <row r="23">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>7803968.857906403</v>
+        <v>7827507.424831179</v>
       </c>
     </row>
     <row r="24">
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>4054009.796315014</v>
+        <v>4066237.623288925</v>
       </c>
     </row>
     <row r="25">
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>20742341.12284577</v>
+        <v>20804904.79955778</v>
       </c>
     </row>
     <row r="27">
@@ -728,7 +728,7 @@
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>8839092.692565504</v>
+        <v>8865753.431310952</v>
       </c>
     </row>
     <row r="28">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>14010.65785606469</v>
+        <v>14052.91722608652</v>
       </c>
     </row>
     <row r="32">
@@ -768,7 +768,7 @@
         </is>
       </c>
       <c r="B32" s="6" t="n">
-        <v>6713.440222697664</v>
+        <v>6733.689504166458</v>
       </c>
     </row>
     <row r="33">
@@ -778,7 +778,7 @@
         </is>
       </c>
       <c r="B33" s="6" t="n">
-        <v>7297.217633367027</v>
+        <v>7319.227721920064</v>
       </c>
     </row>
     <row r="34">
@@ -868,16 +868,16 @@
         </is>
       </c>
       <c r="B2" s="11" t="n">
-        <v>17182</v>
+        <v>17179</v>
       </c>
       <c r="C2" s="11" t="n">
         <v>110267</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>1760415</v>
+        <v>1770843</v>
       </c>
       <c r="F2" s="11" t="n">
         <v>2281</v>
@@ -893,22 +893,22 @@
         </is>
       </c>
       <c r="B3" s="11" t="n">
-        <v>57024</v>
+        <v>57026</v>
       </c>
       <c r="C3" s="11" t="n">
         <v>110263</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>4679</v>
+        <v>4685</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>10673739</v>
+        <v>10687449</v>
       </c>
       <c r="F3" s="11" t="n">
         <v>2281</v>
       </c>
       <c r="G3" s="12" t="n">
-        <v>33.4</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="4">
@@ -924,16 +924,16 @@
         <v>110317</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>4200</v>
+        <v>4143</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>9580498</v>
+        <v>9450131</v>
       </c>
       <c r="F4" s="11" t="n">
         <v>2281</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>30</v>
+        <v>29.5</v>
       </c>
     </row>
     <row r="5">
@@ -949,16 +949,16 @@
         <v>110231</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>2739</v>
+        <v>2836</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>6247330</v>
+        <v>6469878</v>
       </c>
       <c r="F5" s="11" t="n">
         <v>2281</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>19.5</v>
+        <v>20.2</v>
       </c>
     </row>
     <row r="6">
@@ -974,16 +974,16 @@
         <v>110343</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>1622</v>
+        <v>1613</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>3699833</v>
+        <v>3679916</v>
       </c>
       <c r="F6" s="11" t="n">
         <v>2281</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
     </row>
   </sheetData>
@@ -1047,19 +1047,19 @@
         </is>
       </c>
       <c r="B2" s="11" t="n">
-        <v>6382030</v>
+        <v>6932610</v>
       </c>
       <c r="C2" s="11" t="n">
-        <v>2010777</v>
+        <v>2184247</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>4371253</v>
+        <v>4748363</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>2161457</v>
+        <v>2347927</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>2798</v>
+        <v>3039</v>
       </c>
     </row>
     <row r="3">
@@ -1069,19 +1069,19 @@
         </is>
       </c>
       <c r="B3" s="11" t="n">
-        <v>21904984</v>
+        <v>21175095</v>
       </c>
       <c r="C3" s="11" t="n">
-        <v>6901570</v>
+        <v>6671605</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>15003414</v>
+        <v>14503490</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>4090900</v>
+        <v>3954588</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>9602</v>
+        <v>9282</v>
       </c>
     </row>
     <row r="4">
@@ -1091,19 +1091,19 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>2171819</v>
+        <v>2288733</v>
       </c>
       <c r="C4" s="11" t="n">
-        <v>684272</v>
+        <v>721108</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>1487547</v>
+        <v>1567625</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>1252137</v>
+        <v>1319542</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>952</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="5">
@@ -1113,19 +1113,19 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>1502980</v>
+        <v>1661779</v>
       </c>
       <c r="C5" s="11" t="n">
-        <v>473542</v>
+        <v>523574</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>1029439</v>
+        <v>1138205</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>740584</v>
+        <v>818204</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>659</v>
+        <v>728</v>
       </c>
     </row>
   </sheetData>
@@ -1255,34 +1255,34 @@
         <v>4500</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>31961813</v>
+        <v>32058217</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>10070160</v>
+        <v>10100534</v>
       </c>
       <c r="G3" s="11" t="n">
-        <v>21891653</v>
+        <v>21957683</v>
       </c>
       <c r="H3" s="11" t="n">
-        <v>2556945</v>
+        <v>2564657</v>
       </c>
       <c r="I3" s="11" t="n">
-        <v>34518758</v>
+        <v>34622875</v>
       </c>
       <c r="J3" s="11" t="n">
-        <v>19177088</v>
+        <v>19234930</v>
       </c>
       <c r="K3" s="11" t="n">
-        <v>40751920</v>
+        <v>40874837</v>
       </c>
       <c r="L3" s="11" t="n">
-        <v>14011</v>
+        <v>14053</v>
       </c>
       <c r="M3" s="11" t="n">
         <v>2281</v>
       </c>
       <c r="N3" s="11" t="n">
-        <v>13258639</v>
+        <v>13298630</v>
       </c>
     </row>
     <row r="4">
@@ -1303,34 +1303,34 @@
         <v>4500</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>53259558</v>
+        <v>53214714</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>16780409</v>
+        <v>16766280</v>
       </c>
       <c r="G4" s="11" t="n">
-        <v>36479149</v>
+        <v>36448435</v>
       </c>
       <c r="H4" s="11" t="n">
-        <v>4260765</v>
+        <v>4257177</v>
       </c>
       <c r="I4" s="11" t="n">
-        <v>57520322</v>
+        <v>57471892</v>
       </c>
       <c r="J4" s="11" t="n">
-        <v>31955735</v>
+        <v>31928829</v>
       </c>
       <c r="K4" s="11" t="n">
-        <v>67906949</v>
+        <v>67849773</v>
       </c>
       <c r="L4" s="11" t="n">
-        <v>23347</v>
+        <v>23327</v>
       </c>
       <c r="M4" s="11" t="n">
         <v>2281</v>
       </c>
       <c r="N4" s="11" t="n">
-        <v>22093529</v>
+        <v>22074927</v>
       </c>
     </row>
     <row r="5">
@@ -1351,34 +1351,34 @@
         <v>7500</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>89738707</v>
+        <v>89663149</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>16780409</v>
+        <v>16766280</v>
       </c>
       <c r="G5" s="11" t="n">
-        <v>72958298</v>
+        <v>72896869</v>
       </c>
       <c r="H5" s="11" t="n">
-        <v>7179097</v>
+        <v>7173052</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>96917803</v>
+        <v>96836201</v>
       </c>
       <c r="J5" s="11" t="n">
-        <v>53843224</v>
+        <v>53797889</v>
       </c>
       <c r="K5" s="11" t="n">
-        <v>114417864</v>
+        <v>114321527</v>
       </c>
       <c r="L5" s="11" t="n">
-        <v>23347</v>
+        <v>23327</v>
       </c>
       <c r="M5" s="11" t="n">
         <v>3844</v>
       </c>
       <c r="N5" s="11" t="n">
-        <v>24457918</v>
+        <v>24437325</v>
       </c>
     </row>
   </sheetData>
@@ -1453,19 +1453,19 @@
         </is>
       </c>
       <c r="C2" s="11" t="n">
-        <v>6382030</v>
+        <v>6932610</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>2010777</v>
+        <v>2184247</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>4371253</v>
+        <v>4748363</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>2161457</v>
+        <v>2347927</v>
       </c>
       <c r="G2" s="11" t="n">
-        <v>2798</v>
+        <v>3039</v>
       </c>
     </row>
     <row r="3">
@@ -1480,19 +1480,19 @@
         </is>
       </c>
       <c r="C3" s="11" t="n">
-        <v>21904984</v>
+        <v>21175095</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>6901570</v>
+        <v>6671605</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>15003414</v>
+        <v>14503490</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>4090900</v>
+        <v>3954588</v>
       </c>
       <c r="G3" s="11" t="n">
-        <v>9602</v>
+        <v>9282</v>
       </c>
     </row>
     <row r="4">
@@ -1507,19 +1507,19 @@
         </is>
       </c>
       <c r="C4" s="11" t="n">
-        <v>2171819</v>
+        <v>2288733</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>684272</v>
+        <v>721108</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>1487547</v>
+        <v>1567625</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>1252137</v>
+        <v>1319542</v>
       </c>
       <c r="G4" s="11" t="n">
-        <v>952</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="5">
@@ -1534,19 +1534,19 @@
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>1502980</v>
+        <v>1661779</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>473542</v>
+        <v>523574</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>1029439</v>
+        <v>1138205</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>740584</v>
+        <v>818204</v>
       </c>
       <c r="G5" s="11" t="n">
-        <v>659</v>
+        <v>728</v>
       </c>
     </row>
     <row r="6">
@@ -1561,19 +1561,19 @@
         </is>
       </c>
       <c r="C6" s="11" t="n">
-        <v>6382030</v>
+        <v>6932610</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>2010777</v>
+        <v>2184247</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>4371253</v>
+        <v>4748363</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>2161457</v>
+        <v>2347927</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>2798</v>
+        <v>3039</v>
       </c>
     </row>
     <row r="7">
@@ -1588,19 +1588,19 @@
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>39410501</v>
+        <v>38097316</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>12417007</v>
+        <v>12003264</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>26993494</v>
+        <v>26094052</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>6103700</v>
+        <v>5900320</v>
       </c>
       <c r="G7" s="11" t="n">
-        <v>17276</v>
+        <v>16700</v>
       </c>
     </row>
     <row r="8">
@@ -1615,19 +1615,19 @@
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>2171819</v>
+        <v>2288733</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>684272</v>
+        <v>721108</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>1487547</v>
+        <v>1567625</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>1252137</v>
+        <v>1319542</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>952</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="9">
@@ -1642,19 +1642,19 @@
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>5295208</v>
+        <v>5896055</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>1668353</v>
+        <v>1857661</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>3626855</v>
+        <v>4038394</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>2673560</v>
+        <v>2981944</v>
       </c>
       <c r="G9" s="11" t="n">
-        <v>2321</v>
+        <v>2585</v>
       </c>
     </row>
     <row r="10">
@@ -1669,19 +1669,19 @@
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>10753283</v>
+        <v>11680974</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>2010777</v>
+        <v>2184247</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>8742507</v>
+        <v>9496727</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>3641907</v>
+        <v>3956096</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>2798</v>
+        <v>3039</v>
       </c>
     </row>
     <row r="11">
@@ -1696,19 +1696,19 @@
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>66403995</v>
+        <v>64191369</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>12417007</v>
+        <v>12003264</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>53986988</v>
+        <v>52188105</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>10284316</v>
+        <v>9941636</v>
       </c>
       <c r="G11" s="11" t="n">
-        <v>17276</v>
+        <v>16700</v>
       </c>
     </row>
     <row r="12">
@@ -1723,19 +1723,19 @@
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>3659366</v>
+        <v>3856358</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>684272</v>
+        <v>721108</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>2975094</v>
+        <v>3135250</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>2109765</v>
+        <v>2223339</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>952</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="13">
@@ -1750,19 +1750,19 @@
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>8922063</v>
+        <v>9934449</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>1668353</v>
+        <v>1857661</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>7253710</v>
+        <v>8076788</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>4504766</v>
+        <v>5024372</v>
       </c>
       <c r="G13" s="11" t="n">
-        <v>2321</v>
+        <v>2585</v>
       </c>
     </row>
   </sheetData>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12,755 -&gt; 14,127</t>
+          <t>12,755 -&gt; 14,126</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2080,7 +2080,7 @@
     <row r="3">
       <c r="A3" s="14" t="inlineStr">
         <is>
-          <t>Both arms are driven by OBSERVED births — the count of age-0 dependents in each PUMS tax unit (an infant &lt;1yr ≈ a birth in the last 12 months, the annual flow). The weighted count is calibrated to CDC NVSR resident births (by-residence basis, 2022=15,535), then projected to 2028 with the repo's damped-trend ensemble (point 14,127, 90% PI [13,071, 15,183]). NVSR finals run through 2024; later years are nowcast from Hawaiʻi DOH preliminary births (snapshot 2026-07-06) converted occurrence→residence at ÷1.0055 (sd 0.0050, carried into their MOEs): 2025≈14,499; 2026≈14,374 (annualised from 5mo). Each birth draws one prenatal + one postnatal payment. This replaces the legacy num_dependents × rate proxy, which multiplied an all-dependents count (incl. older children, students, adult dependents) by a children-only-calibrated rate and overstated total births ~1.7×. County split: recalibrated to Hawaiʻi DOH's aggregate county vital-statistics shares (2018-2025), not raw PUMS county shares — PUMS's own county allocation is small-sample-noisy (Hawaii County carries only ~11 sampled infants) and Maui/Kauai are not independently sampled at all (one combined PUMA, split by a demographic-heuristic imputer, not survey evidence). Per-county factor vs the raw PUMS-implied count: Honolulu×0.96; Hawaii×1.41; Maui×1.03; Kauai×0.92. The state BIRTH total is unchanged (redistribution only), but the state COST total is NOT — eligibility is unit-specific and correlated with county, so this also corrects the eligible share (measured +2.1% on cost/recipients on the real frame; eligible_families itself is unchanged). --no-doh-county-shares restores raw PUMS shares. Cost = the take-up-adjusted benefit weighted by the household (WGTP) weight, summed to SPM-unit grain. Per-unit amounts are expectations, not literal payments.</t>
+          <t>Both arms are driven by OBSERVED births — the count of age-0 dependents in each PUMS tax unit (an infant &lt;1yr ≈ a birth in the last 12 months, the annual flow). The weighted count is calibrated to CDC NVSR resident births (by-residence basis, 2022=15,535), then projected to 2028 with the repo's damped-trend ensemble (point 14,126, 90% PI [12,868, 15,384]). NVSR finals run through 2024; later years are nowcast from Hawaiʻi DOH preliminary births (snapshot 2026-07-06) converted occurrence→residence at ÷1.0026 (sd 0.0007, carried into their MOEs): 2025≈14,541; 2026≈14,416 (annualised from 5mo). Each birth draws one prenatal + one postnatal payment. This replaces the legacy num_dependents × rate proxy, which multiplied an all-dependents count (incl. older children, students, adult dependents) by a children-only-calibrated rate and overstated total births ~1.7×. County split: recalibrated to CDC WONDER county-of-RESIDENCE natality shares (2020-2024), not raw PUMS county shares — PUMS's own county allocation is small-sample-noisy (Hawaii County carries only ~11 sampled infants) and Maui/Kauai are not independently sampled at all (one combined PUMA, split by a demographic-heuristic imputer, not survey evidence). Residence basis matters here: DOH's occurrence counts overstate Honolulu ~2.2pp because neighbour-island mothers deliver on Oʻahu. Per-county factor vs the raw PUMS-implied count: Honolulu×0.92; Hawaii×1.53; Maui×1.15; Kauai×0.97. The state BIRTH total is unchanged (redistribution only), but the state COST total is NOT — eligibility is unit-specific and correlated with county, so this also corrects the eligible share (eligible_families itself is unchanged). --no-county-share-calibration restores raw PUMS shares. Cost = the take-up-adjusted benefit weighted by the household (WGTP) weight, summed to SPM-unit grain. Per-unit amounts are expectations, not literal payments.</t>
         </is>
       </c>
     </row>

--- a/reports/rxkids_2028/rxkids_2028_cost_and_impact.xlsx
+++ b/reports/rxkids_2028/rxkids_2028_cost_and_impact.xlsx
@@ -528,7 +528,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>32058217.42200988</v>
+        <v>31413985.55069333</v>
       </c>
     </row>
     <row r="6">
@@ -538,7 +538,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>10100534.25624969</v>
+        <v>9897557.091314334</v>
       </c>
     </row>
     <row r="7">
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>21957683.16576019</v>
+        <v>21516428.45937899</v>
       </c>
     </row>
     <row r="8">
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>2564657.39376079</v>
+        <v>2513118.844055466</v>
       </c>
     </row>
     <row r="9">
@@ -568,7 +568,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>34622874.81577067</v>
+        <v>33927104.39474879</v>
       </c>
     </row>
     <row r="10">
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>24364840.04645819</v>
+        <v>23875211.87122842</v>
       </c>
     </row>
     <row r="11">
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>39751594.79756156</v>
+        <v>38952759.23015823</v>
       </c>
     </row>
     <row r="12">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>4676825.152311054</v>
+        <v>4582841.14253186</v>
       </c>
     </row>
     <row r="13">
@@ -608,7 +608,7 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>19234930.45320593</v>
+        <v>18848391.33041599</v>
       </c>
     </row>
     <row r="14">
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>40874837.14870609</v>
+        <v>40053429.25570231</v>
       </c>
     </row>
     <row r="15">
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>21957683.1657602</v>
+        <v>21516428.459379</v>
       </c>
     </row>
     <row r="18">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>54015900.58777007</v>
+        <v>52930414.01007232</v>
       </c>
     </row>
     <row r="19">
@@ -668,7 +668,7 @@
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>13298630.14696643</v>
+        <v>13031385.051185</v>
       </c>
     </row>
     <row r="22">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>5471122.722135249</v>
+        <v>5361176.757795264</v>
       </c>
     </row>
     <row r="23">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>7827507.424831179</v>
+        <v>7670208.293389732</v>
       </c>
     </row>
     <row r="24">
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>4066237.623288925</v>
+        <v>3984523.788773885</v>
       </c>
     </row>
     <row r="25">
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>20804904.79955778</v>
+        <v>20386815.96526159</v>
       </c>
     </row>
     <row r="27">
@@ -728,7 +728,7 @@
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>8865753.431310952</v>
+        <v>8687590.034123331</v>
       </c>
     </row>
     <row r="28">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>14052.91722608652</v>
+        <v>13770.51421400255</v>
       </c>
     </row>
     <row r="32">
@@ -768,7 +768,7 @@
         </is>
       </c>
       <c r="B32" s="6" t="n">
-        <v>6733.689504166458</v>
+        <v>6598.371394209556</v>
       </c>
     </row>
     <row r="33">
@@ -778,7 +778,7 @@
         </is>
       </c>
       <c r="B33" s="6" t="n">
-        <v>7319.227721920064</v>
+        <v>7172.142819792996</v>
       </c>
     </row>
     <row r="34">
@@ -868,16 +868,16 @@
         </is>
       </c>
       <c r="B2" s="11" t="n">
-        <v>17179</v>
+        <v>17182</v>
       </c>
       <c r="C2" s="11" t="n">
         <v>110267</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>776</v>
+        <v>761</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>1770843</v>
+        <v>1735257</v>
       </c>
       <c r="F2" s="11" t="n">
         <v>2281</v>
@@ -893,16 +893,16 @@
         </is>
       </c>
       <c r="B3" s="11" t="n">
-        <v>57026</v>
+        <v>57028</v>
       </c>
       <c r="C3" s="11" t="n">
         <v>110263</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>4685</v>
+        <v>4591</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>10687449</v>
+        <v>10472677</v>
       </c>
       <c r="F3" s="11" t="n">
         <v>2281</v>
@@ -924,10 +924,10 @@
         <v>110317</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>4143</v>
+        <v>4059</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>9450131</v>
+        <v>9260225</v>
       </c>
       <c r="F4" s="11" t="n">
         <v>2281</v>
@@ -949,10 +949,10 @@
         <v>110231</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>2836</v>
+        <v>2779</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>6469878</v>
+        <v>6339862</v>
       </c>
       <c r="F5" s="11" t="n">
         <v>2281</v>
@@ -974,10 +974,10 @@
         <v>110343</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>1613</v>
+        <v>1581</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>3679916</v>
+        <v>3605966</v>
       </c>
       <c r="F6" s="11" t="n">
         <v>2281</v>
@@ -1047,19 +1047,19 @@
         </is>
       </c>
       <c r="B2" s="11" t="n">
-        <v>6932610</v>
+        <v>6793295</v>
       </c>
       <c r="C2" s="11" t="n">
-        <v>2184247</v>
+        <v>2140353</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>4748363</v>
+        <v>4652942</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>2347927</v>
+        <v>2300744</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>3039</v>
+        <v>2978</v>
       </c>
     </row>
     <row r="3">
@@ -1069,19 +1069,19 @@
         </is>
       </c>
       <c r="B3" s="11" t="n">
-        <v>21175095</v>
+        <v>20749567</v>
       </c>
       <c r="C3" s="11" t="n">
-        <v>6671605</v>
+        <v>6537535</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>14503490</v>
+        <v>14212032</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>3954588</v>
+        <v>3875118</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>9282</v>
+        <v>9096</v>
       </c>
     </row>
     <row r="4">
@@ -1091,19 +1091,19 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>2288733</v>
+        <v>2242739</v>
       </c>
       <c r="C4" s="11" t="n">
-        <v>721108</v>
+        <v>706616</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>1567625</v>
+        <v>1536123</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>1319542</v>
+        <v>1293025</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>1003</v>
+        <v>983</v>
       </c>
     </row>
     <row r="5">
@@ -1113,19 +1113,19 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>1661779</v>
+        <v>1628384</v>
       </c>
       <c r="C5" s="11" t="n">
-        <v>523574</v>
+        <v>513053</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>1138205</v>
+        <v>1115332</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>818204</v>
+        <v>801762</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>728</v>
+        <v>714</v>
       </c>
     </row>
   </sheetData>
@@ -1255,34 +1255,34 @@
         <v>4500</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>32058217</v>
+        <v>31413986</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>10100534</v>
+        <v>9897557</v>
       </c>
       <c r="G3" s="11" t="n">
-        <v>21957683</v>
+        <v>21516428</v>
       </c>
       <c r="H3" s="11" t="n">
-        <v>2564657</v>
+        <v>2513119</v>
       </c>
       <c r="I3" s="11" t="n">
-        <v>34622875</v>
+        <v>33927104</v>
       </c>
       <c r="J3" s="11" t="n">
-        <v>19234930</v>
+        <v>18848391</v>
       </c>
       <c r="K3" s="11" t="n">
-        <v>40874837</v>
+        <v>40053429</v>
       </c>
       <c r="L3" s="11" t="n">
-        <v>14053</v>
+        <v>13771</v>
       </c>
       <c r="M3" s="11" t="n">
         <v>2281</v>
       </c>
       <c r="N3" s="11" t="n">
-        <v>13298630</v>
+        <v>13031385</v>
       </c>
     </row>
     <row r="4">
@@ -1303,34 +1303,34 @@
         <v>4500</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>53214714</v>
+        <v>52145328</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>16766280</v>
+        <v>16429350</v>
       </c>
       <c r="G4" s="11" t="n">
-        <v>36448435</v>
+        <v>35715978</v>
       </c>
       <c r="H4" s="11" t="n">
-        <v>4257177</v>
+        <v>4171626</v>
       </c>
       <c r="I4" s="11" t="n">
-        <v>57471892</v>
+        <v>56316954</v>
       </c>
       <c r="J4" s="11" t="n">
-        <v>31928829</v>
+        <v>31287197</v>
       </c>
       <c r="K4" s="11" t="n">
-        <v>67849773</v>
+        <v>66486286</v>
       </c>
       <c r="L4" s="11" t="n">
-        <v>23327</v>
+        <v>22858</v>
       </c>
       <c r="M4" s="11" t="n">
         <v>2281</v>
       </c>
       <c r="N4" s="11" t="n">
-        <v>22074927</v>
+        <v>21631316</v>
       </c>
     </row>
     <row r="5">
@@ -1351,34 +1351,34 @@
         <v>7500</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>89663149</v>
+        <v>87861306</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>16766280</v>
+        <v>16429350</v>
       </c>
       <c r="G5" s="11" t="n">
-        <v>72896869</v>
+        <v>71431956</v>
       </c>
       <c r="H5" s="11" t="n">
-        <v>7173052</v>
+        <v>7028905</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>96836201</v>
+        <v>94890211</v>
       </c>
       <c r="J5" s="11" t="n">
-        <v>53797889</v>
+        <v>52716784</v>
       </c>
       <c r="K5" s="11" t="n">
-        <v>114321527</v>
+        <v>112024158</v>
       </c>
       <c r="L5" s="11" t="n">
-        <v>23327</v>
+        <v>22858</v>
       </c>
       <c r="M5" s="11" t="n">
         <v>3844</v>
       </c>
       <c r="N5" s="11" t="n">
-        <v>24437325</v>
+        <v>23946241</v>
       </c>
     </row>
   </sheetData>
@@ -1453,19 +1453,19 @@
         </is>
       </c>
       <c r="C2" s="11" t="n">
-        <v>6932610</v>
+        <v>6793295</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>2184247</v>
+        <v>2140353</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>4748363</v>
+        <v>4652942</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>2347927</v>
+        <v>2300744</v>
       </c>
       <c r="G2" s="11" t="n">
-        <v>3039</v>
+        <v>2978</v>
       </c>
     </row>
     <row r="3">
@@ -1480,19 +1480,19 @@
         </is>
       </c>
       <c r="C3" s="11" t="n">
-        <v>21175095</v>
+        <v>20749567</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>6671605</v>
+        <v>6537535</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>14503490</v>
+        <v>14212032</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>3954588</v>
+        <v>3875118</v>
       </c>
       <c r="G3" s="11" t="n">
-        <v>9282</v>
+        <v>9096</v>
       </c>
     </row>
     <row r="4">
@@ -1507,19 +1507,19 @@
         </is>
       </c>
       <c r="C4" s="11" t="n">
-        <v>2288733</v>
+        <v>2242739</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>721108</v>
+        <v>706616</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>1567625</v>
+        <v>1536123</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>1319542</v>
+        <v>1293025</v>
       </c>
       <c r="G4" s="11" t="n">
-        <v>1003</v>
+        <v>983</v>
       </c>
     </row>
     <row r="5">
@@ -1534,19 +1534,19 @@
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>1661779</v>
+        <v>1628384</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>523574</v>
+        <v>513053</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>1138205</v>
+        <v>1115332</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>818204</v>
+        <v>801762</v>
       </c>
       <c r="G5" s="11" t="n">
-        <v>728</v>
+        <v>714</v>
       </c>
     </row>
     <row r="6">
@@ -1561,19 +1561,19 @@
         </is>
       </c>
       <c r="C6" s="11" t="n">
-        <v>6932610</v>
+        <v>6793295</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>2184247</v>
+        <v>2140353</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>4748363</v>
+        <v>4652942</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>2347927</v>
+        <v>2300744</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>3039</v>
+        <v>2978</v>
       </c>
     </row>
     <row r="7">
@@ -1588,19 +1588,19 @@
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>38097316</v>
+        <v>37331725</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>12003264</v>
+        <v>11762050</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>26094052</v>
+        <v>25569674</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>5900320</v>
+        <v>5781749</v>
       </c>
       <c r="G7" s="11" t="n">
-        <v>16700</v>
+        <v>16365</v>
       </c>
     </row>
     <row r="8">
@@ -1615,19 +1615,19 @@
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>2288733</v>
+        <v>2242739</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>721108</v>
+        <v>706616</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>1567625</v>
+        <v>1536123</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>1319542</v>
+        <v>1293025</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>1003</v>
+        <v>983</v>
       </c>
     </row>
     <row r="9">
@@ -1642,19 +1642,19 @@
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>5896055</v>
+        <v>5777570</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>1857661</v>
+        <v>1820330</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>4038394</v>
+        <v>3957240</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>2981944</v>
+        <v>2922020</v>
       </c>
       <c r="G9" s="11" t="n">
-        <v>2585</v>
+        <v>2533</v>
       </c>
     </row>
     <row r="10">
@@ -1669,19 +1669,19 @@
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>11680974</v>
+        <v>11446236</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>2184247</v>
+        <v>2140353</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>9496727</v>
+        <v>9305883</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>3956096</v>
+        <v>3876596</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>3039</v>
+        <v>2978</v>
       </c>
     </row>
     <row r="11">
@@ -1696,19 +1696,19 @@
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>64191369</v>
+        <v>62901399</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>12003264</v>
+        <v>11762050</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>52188105</v>
+        <v>51139349</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>9941636</v>
+        <v>9741852</v>
       </c>
       <c r="G11" s="11" t="n">
-        <v>16700</v>
+        <v>16365</v>
       </c>
     </row>
     <row r="12">
@@ -1723,19 +1723,19 @@
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>3856358</v>
+        <v>3778862</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>721108</v>
+        <v>706616</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>3135250</v>
+        <v>3072245</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>2223339</v>
+        <v>2178659</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>1003</v>
+        <v>983</v>
       </c>
     </row>
     <row r="13">
@@ -1750,19 +1750,19 @@
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>9934449</v>
+        <v>9734809</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>1857661</v>
+        <v>1820330</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>8076788</v>
+        <v>7914479</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>5024372</v>
+        <v>4923404</v>
       </c>
       <c r="G13" s="11" t="n">
-        <v>2585</v>
+        <v>2533</v>
       </c>
     </row>
   </sheetData>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12,755 -&gt; 14,126</t>
+          <t>12,755 -&gt; 13,842</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2080,7 +2080,7 @@
     <row r="3">
       <c r="A3" s="14" t="inlineStr">
         <is>
-          <t>Both arms are driven by OBSERVED births — the count of age-0 dependents in each PUMS tax unit (an infant &lt;1yr ≈ a birth in the last 12 months, the annual flow). The weighted count is calibrated to CDC NVSR resident births (by-residence basis, 2022=15,535), then projected to 2028 with the repo's damped-trend ensemble (point 14,126, 90% PI [12,868, 15,384]). NVSR finals run through 2024; later years are nowcast from Hawaiʻi DOH preliminary births (snapshot 2026-07-06) converted occurrence→residence at ÷1.0026 (sd 0.0007, carried into their MOEs): 2025≈14,541; 2026≈14,416 (annualised from 5mo). Each birth draws one prenatal + one postnatal payment. This replaces the legacy num_dependents × rate proxy, which multiplied an all-dependents count (incl. older children, students, adult dependents) by a children-only-calibrated rate and overstated total births ~1.7×. County split: recalibrated to CDC WONDER county-of-RESIDENCE natality shares (2020-2024), not raw PUMS county shares — PUMS's own county allocation is small-sample-noisy (Hawaii County carries only ~11 sampled infants) and Maui/Kauai are not independently sampled at all (one combined PUMA, split by a demographic-heuristic imputer, not survey evidence). Residence basis matters here: DOH's occurrence counts overstate Honolulu ~2.2pp because neighbour-island mothers deliver on Oʻahu. Per-county factor vs the raw PUMS-implied count: Honolulu×0.92; Hawaii×1.53; Maui×1.15; Kauai×0.97. The state BIRTH total is unchanged (redistribution only), but the state COST total is NOT — eligibility is unit-specific and correlated with county, so this also corrects the eligible share (eligible_families itself is unchanged). --no-county-share-calibration restores raw PUMS shares. Cost = the take-up-adjusted benefit weighted by the household (WGTP) weight, summed to SPM-unit grain. Per-unit amounts are expectations, not literal payments.</t>
+          <t>Both arms are driven by OBSERVED births — the count of age-0 dependents in each PUMS tax unit (an infant &lt;1yr ≈ a birth in the last 12 months, the annual flow). The weighted count is calibrated to CDC NVSR resident births (by-residence basis, 2022=15,535), then projected to 2028 with the repo's damped-trend ensemble (point 13,842, 90% PI [12,779, 14,905]). NVSR finals run through 2024; later years are nowcast from Hawaiʻi DOH preliminary births (snapshot 2026-07-06) converted occurrence→residence at ÷1.0026 (sd 0.0007, carried into their MOEs): 2025≈14,541; 2026≈14,416 (annualised from 5mo). Each birth draws one prenatal + one postnatal payment. This replaces the legacy num_dependents × rate proxy, which multiplied an all-dependents count (incl. older children, students, adult dependents) by a children-only-calibrated rate and overstated total births ~1.7×. County split: recalibrated to CDC WONDER county-of-RESIDENCE natality shares (2020-2024), not raw PUMS county shares — PUMS's own county allocation is small-sample-noisy (Hawaii County carries only ~11 sampled infants) and Maui/Kauai are not independently sampled at all (one combined PUMA, split by a demographic-heuristic imputer, not survey evidence). Residence basis matters here: DOH's occurrence counts overstate Honolulu ~2.2pp because neighbour-island mothers deliver on Oʻahu. Per-county factor vs the raw PUMS-implied count: Honolulu×0.92; Hawaii×1.53; Maui×1.15; Kauai×0.97. The state BIRTH total is unchanged (redistribution only), but the state COST total is NOT — eligibility is unit-specific and correlated with county, so this also corrects the eligible share (eligible_families itself is unchanged). --no-county-share-calibration restores raw PUMS shares. Cost = the take-up-adjusted benefit weighted by the household (WGTP) weight, summed to SPM-unit grain. Per-unit amounts are expectations, not literal payments.</t>
         </is>
       </c>
     </row>

--- a/reports/rxkids_2028/rxkids_2028_cost_and_impact.xlsx
+++ b/reports/rxkids_2028/rxkids_2028_cost_and_impact.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B36"/>
+  <dimension ref="A1:B37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -528,7 +528,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>31413985.55069333</v>
+        <v>20655771.32100383</v>
       </c>
     </row>
     <row r="6">
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>21516428.45937899</v>
+        <v>10758214.22968949</v>
       </c>
     </row>
     <row r="8">
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>2513118.844055466</v>
+        <v>1652461.705680307</v>
       </c>
     </row>
     <row r="9">
@@ -568,7 +568,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>33927104.39474879</v>
+        <v>22308233.02668414</v>
       </c>
     </row>
     <row r="10">
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>23875211.87122842</v>
+        <v>15698769.44957485</v>
       </c>
     </row>
     <row r="11">
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>38952759.23015823</v>
+        <v>25612773.19243281</v>
       </c>
     </row>
     <row r="12">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>4582841.14253186</v>
+        <v>3013374.997829169</v>
       </c>
     </row>
     <row r="13">
@@ -608,7 +608,7 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>18848391.33041599</v>
+        <v>12393462.7926023</v>
       </c>
     </row>
     <row r="14">
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>40053429.25570231</v>
+        <v>26336706.1128482</v>
       </c>
     </row>
     <row r="15">
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>21516428.459379</v>
+        <v>32274642.68906849</v>
       </c>
     </row>
     <row r="18">
@@ -668,7 +668,7 @@
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>13031385.051185</v>
+        <v>10316928.22008279</v>
       </c>
     </row>
     <row r="22">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>7670208.293389732</v>
+        <v>4955751.462287521</v>
       </c>
     </row>
     <row r="24">
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>3984523.788773885</v>
+        <v>871614.5787942875</v>
       </c>
     </row>
     <row r="25">
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="B25" s="8" t="n">
-        <v>41.5</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="26">
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>20386815.96526159</v>
+        <v>15455967.7766539</v>
       </c>
     </row>
     <row r="27">
@@ -728,7 +728,7 @@
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>8687590.034123331</v>
+        <v>6877952.146721857</v>
       </c>
     </row>
     <row r="28">
@@ -744,58 +744,68 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>Eligible families (weighted)</t>
+          <t>Births served / year (people affected)</t>
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>7340</v>
+        <v>7969.047577547773</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
+          <t>Eligible families (weighted)</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n">
+        <v>7340</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
           <t>Expected recipients / year</t>
         </is>
       </c>
-      <c r="B31" s="6" t="n">
+      <c r="B32" s="6" t="n">
         <v>13770.51421400255</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Expected pregnancies (prenatal)</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="n">
-        <v>6598.371394209556</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">  Expected pregnancies (prenatal)</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n">
+        <v>6598.371394209556</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">  Expected infants (postnatal)</t>
         </is>
       </c>
-      <c r="B33" s="6" t="n">
+      <c r="B34" s="6" t="n">
         <v>7172.142819792996</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>Avg benefit per recipient</t>
         </is>
       </c>
-      <c r="B34" s="6" t="n">
-        <v>2281.25</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr"/>
+      <c r="B35" s="6" t="n">
+        <v>1500</v>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
+      <c r="A36" s="4" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>Benefits by income quintile → see the 'By income quintile' tab.</t>
         </is>
@@ -877,10 +887,10 @@
         <v>761</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>1735257</v>
+        <v>1140991</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>2281</v>
+        <v>1500</v>
       </c>
       <c r="G2" s="12" t="n">
         <v>5.5</v>
@@ -893,7 +903,7 @@
         </is>
       </c>
       <c r="B3" s="11" t="n">
-        <v>57028</v>
+        <v>57024</v>
       </c>
       <c r="C3" s="11" t="n">
         <v>110263</v>
@@ -902,10 +912,10 @@
         <v>4591</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>10472677</v>
+        <v>6886144</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>2281</v>
+        <v>1500</v>
       </c>
       <c r="G3" s="12" t="n">
         <v>33.3</v>
@@ -927,10 +937,10 @@
         <v>4059</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>9260225</v>
+        <v>6088915</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>2281</v>
+        <v>1500</v>
       </c>
       <c r="G4" s="12" t="n">
         <v>29.5</v>
@@ -952,10 +962,10 @@
         <v>2779</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>6339862</v>
+        <v>4168676</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>2281</v>
+        <v>1500</v>
       </c>
       <c r="G5" s="12" t="n">
         <v>20.2</v>
@@ -968,7 +978,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>334087</v>
+        <v>334084</v>
       </c>
       <c r="C6" s="11" t="n">
         <v>110343</v>
@@ -977,10 +987,10 @@
         <v>1581</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>3605966</v>
+        <v>2371046</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>2281</v>
+        <v>1500</v>
       </c>
       <c r="G6" s="12" t="n">
         <v>11.5</v>
@@ -1047,16 +1057,16 @@
         </is>
       </c>
       <c r="B2" s="11" t="n">
-        <v>6793295</v>
+        <v>4466824</v>
       </c>
       <c r="C2" s="11" t="n">
         <v>2140353</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>4652942</v>
+        <v>2326471</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>2300744</v>
+        <v>1512818</v>
       </c>
       <c r="F2" s="11" t="n">
         <v>2978</v>
@@ -1069,16 +1079,16 @@
         </is>
       </c>
       <c r="B3" s="11" t="n">
-        <v>20749567</v>
+        <v>13643551</v>
       </c>
       <c r="C3" s="11" t="n">
         <v>6537535</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>14212032</v>
+        <v>7106016</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>3875118</v>
+        <v>2548023</v>
       </c>
       <c r="F3" s="11" t="n">
         <v>9096</v>
@@ -1091,16 +1101,16 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>2242739</v>
+        <v>1474678</v>
       </c>
       <c r="C4" s="11" t="n">
         <v>706616</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>1536123</v>
+        <v>768061</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>1293025</v>
+        <v>850208</v>
       </c>
       <c r="F4" s="11" t="n">
         <v>983</v>
@@ -1113,16 +1123,16 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>1628384</v>
+        <v>1070719</v>
       </c>
       <c r="C5" s="11" t="n">
         <v>513053</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>1115332</v>
+        <v>557666</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>801762</v>
+        <v>527186</v>
       </c>
       <c r="F5" s="11" t="n">
         <v>714</v>
@@ -1139,7 +1149,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1240,60 +1250,60 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Statutory (Medicaid OR ≤300% FPL) · 6-mo postnatal</t>
+          <t>Statutory (Medicaid OR &lt;=300% FPL) - 3-mo postnatal</t>
         </is>
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>Medicaid OR ≤300% FPL</t>
+          <t>Medicaid OR &lt;=300% FPL</t>
         </is>
       </c>
       <c r="C3" s="10" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>4500</v>
+        <v>3000</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>31413986</v>
+        <v>20655771</v>
       </c>
       <c r="F3" s="11" t="n">
         <v>9897557</v>
       </c>
       <c r="G3" s="11" t="n">
-        <v>21516428</v>
+        <v>10758214</v>
       </c>
       <c r="H3" s="11" t="n">
-        <v>2513119</v>
+        <v>1652462</v>
       </c>
       <c r="I3" s="11" t="n">
-        <v>33927104</v>
+        <v>22308233</v>
       </c>
       <c r="J3" s="11" t="n">
-        <v>18848391</v>
+        <v>12393463</v>
       </c>
       <c r="K3" s="11" t="n">
-        <v>40053429</v>
+        <v>26336706</v>
       </c>
       <c r="L3" s="11" t="n">
         <v>13771</v>
       </c>
       <c r="M3" s="11" t="n">
-        <v>2281</v>
+        <v>1500</v>
       </c>
       <c r="N3" s="11" t="n">
-        <v>13031385</v>
+        <v>10316928</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
-          <t>Universal · 6-mo postnatal</t>
+          <t>Statutory (Medicaid OR ≤300% FPL) · 6-mo postnatal</t>
         </is>
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>Universal (no income/Medicaid test)</t>
+          <t>Medicaid OR ≤300% FPL</t>
         </is>
       </c>
       <c r="C4" s="10" t="n">
@@ -1303,40 +1313,40 @@
         <v>4500</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>52145328</v>
+        <v>31413986</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>16429350</v>
+        <v>9897557</v>
       </c>
       <c r="G4" s="11" t="n">
-        <v>35715978</v>
+        <v>21516428</v>
       </c>
       <c r="H4" s="11" t="n">
-        <v>4171626</v>
+        <v>2513119</v>
       </c>
       <c r="I4" s="11" t="n">
-        <v>56316954</v>
+        <v>33927104</v>
       </c>
       <c r="J4" s="11" t="n">
-        <v>31287197</v>
+        <v>18848391</v>
       </c>
       <c r="K4" s="11" t="n">
-        <v>66486286</v>
+        <v>40053429</v>
       </c>
       <c r="L4" s="11" t="n">
-        <v>22858</v>
+        <v>13771</v>
       </c>
       <c r="M4" s="11" t="n">
         <v>2281</v>
       </c>
       <c r="N4" s="11" t="n">
-        <v>21631316</v>
+        <v>13031385</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>Universal · 12-mo postnatal</t>
+          <t>Universal · 6-mo postnatal</t>
         </is>
       </c>
       <c r="B5" s="10" t="inlineStr">
@@ -1345,39 +1355,87 @@
         </is>
       </c>
       <c r="C5" s="10" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>7500</v>
+        <v>4500</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>87861306</v>
+        <v>52145328</v>
       </c>
       <c r="F5" s="11" t="n">
         <v>16429350</v>
       </c>
       <c r="G5" s="11" t="n">
-        <v>71431956</v>
+        <v>35715978</v>
       </c>
       <c r="H5" s="11" t="n">
-        <v>7028905</v>
+        <v>4171626</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>94890211</v>
+        <v>56316954</v>
       </c>
       <c r="J5" s="11" t="n">
-        <v>52716784</v>
+        <v>31287197</v>
       </c>
       <c r="K5" s="11" t="n">
-        <v>112024158</v>
+        <v>66486286</v>
       </c>
       <c r="L5" s="11" t="n">
         <v>22858</v>
       </c>
       <c r="M5" s="11" t="n">
+        <v>2281</v>
+      </c>
+      <c r="N5" s="11" t="n">
+        <v>21631316</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>Universal · 12-mo postnatal</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Universal (no income/Medicaid test)</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D6" s="11" t="n">
+        <v>7500</v>
+      </c>
+      <c r="E6" s="11" t="n">
+        <v>87861306</v>
+      </c>
+      <c r="F6" s="11" t="n">
+        <v>16429350</v>
+      </c>
+      <c r="G6" s="11" t="n">
+        <v>71431956</v>
+      </c>
+      <c r="H6" s="11" t="n">
+        <v>7028905</v>
+      </c>
+      <c r="I6" s="11" t="n">
+        <v>94890211</v>
+      </c>
+      <c r="J6" s="11" t="n">
+        <v>52716784</v>
+      </c>
+      <c r="K6" s="11" t="n">
+        <v>112024158</v>
+      </c>
+      <c r="L6" s="11" t="n">
+        <v>22858</v>
+      </c>
+      <c r="M6" s="11" t="n">
         <v>3844</v>
       </c>
-      <c r="N5" s="11" t="n">
+      <c r="N6" s="11" t="n">
         <v>23946241</v>
       </c>
     </row>
@@ -1392,7 +1450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1444,7 +1502,7 @@
     <row r="2">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>Statutory (Medicaid OR ≤300% FPL) · 6-mo postnatal</t>
+          <t>Statutory (Medicaid OR &lt;=300% FPL) - 3-mo postnatal</t>
         </is>
       </c>
       <c r="B2" s="10" t="inlineStr">
@@ -1453,16 +1511,16 @@
         </is>
       </c>
       <c r="C2" s="11" t="n">
-        <v>6793295</v>
+        <v>4466824</v>
       </c>
       <c r="D2" s="11" t="n">
         <v>2140353</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>4652942</v>
+        <v>2326471</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>2300744</v>
+        <v>1512818</v>
       </c>
       <c r="G2" s="11" t="n">
         <v>2978</v>
@@ -1471,7 +1529,7 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Statutory (Medicaid OR ≤300% FPL) · 6-mo postnatal</t>
+          <t>Statutory (Medicaid OR &lt;=300% FPL) - 3-mo postnatal</t>
         </is>
       </c>
       <c r="B3" s="10" t="inlineStr">
@@ -1480,16 +1538,16 @@
         </is>
       </c>
       <c r="C3" s="11" t="n">
-        <v>20749567</v>
+        <v>13643551</v>
       </c>
       <c r="D3" s="11" t="n">
         <v>6537535</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>14212032</v>
+        <v>7106016</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>3875118</v>
+        <v>2548023</v>
       </c>
       <c r="G3" s="11" t="n">
         <v>9096</v>
@@ -1498,7 +1556,7 @@
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
-          <t>Statutory (Medicaid OR ≤300% FPL) · 6-mo postnatal</t>
+          <t>Statutory (Medicaid OR &lt;=300% FPL) - 3-mo postnatal</t>
         </is>
       </c>
       <c r="B4" s="10" t="inlineStr">
@@ -1507,16 +1565,16 @@
         </is>
       </c>
       <c r="C4" s="11" t="n">
-        <v>2242739</v>
+        <v>1474678</v>
       </c>
       <c r="D4" s="11" t="n">
         <v>706616</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>1536123</v>
+        <v>768061</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>1293025</v>
+        <v>850208</v>
       </c>
       <c r="G4" s="11" t="n">
         <v>983</v>
@@ -1525,7 +1583,7 @@
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>Statutory (Medicaid OR ≤300% FPL) · 6-mo postnatal</t>
+          <t>Statutory (Medicaid OR &lt;=300% FPL) - 3-mo postnatal</t>
         </is>
       </c>
       <c r="B5" s="10" t="inlineStr">
@@ -1534,16 +1592,16 @@
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>1628384</v>
+        <v>1070719</v>
       </c>
       <c r="D5" s="11" t="n">
         <v>513053</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>1115332</v>
+        <v>557666</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>801762</v>
+        <v>527186</v>
       </c>
       <c r="G5" s="11" t="n">
         <v>714</v>
@@ -1552,7 +1610,7 @@
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>Universal · 6-mo postnatal</t>
+          <t>Statutory (Medicaid OR ≤300% FPL) · 6-mo postnatal</t>
         </is>
       </c>
       <c r="B6" s="10" t="inlineStr">
@@ -1579,7 +1637,7 @@
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>Universal · 6-mo postnatal</t>
+          <t>Statutory (Medicaid OR ≤300% FPL) · 6-mo postnatal</t>
         </is>
       </c>
       <c r="B7" s="10" t="inlineStr">
@@ -1588,25 +1646,25 @@
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>37331725</v>
+        <v>20749567</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>11762050</v>
+        <v>6537535</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>25569674</v>
+        <v>14212032</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>5781749</v>
+        <v>3875118</v>
       </c>
       <c r="G7" s="11" t="n">
-        <v>16365</v>
+        <v>9096</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>Universal · 6-mo postnatal</t>
+          <t>Statutory (Medicaid OR ≤300% FPL) · 6-mo postnatal</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
@@ -1633,7 +1691,7 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Universal · 6-mo postnatal</t>
+          <t>Statutory (Medicaid OR ≤300% FPL) · 6-mo postnatal</t>
         </is>
       </c>
       <c r="B9" s="10" t="inlineStr">
@@ -1642,25 +1700,25 @@
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>5777570</v>
+        <v>1628384</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>1820330</v>
+        <v>513053</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>3957240</v>
+        <v>1115332</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>2922020</v>
+        <v>801762</v>
       </c>
       <c r="G9" s="11" t="n">
-        <v>2533</v>
+        <v>714</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>Universal · 12-mo postnatal</t>
+          <t>Universal · 6-mo postnatal</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
@@ -1669,16 +1727,16 @@
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>11446236</v>
+        <v>6793295</v>
       </c>
       <c r="D10" s="11" t="n">
         <v>2140353</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>9305883</v>
+        <v>4652942</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>3876596</v>
+        <v>2300744</v>
       </c>
       <c r="G10" s="11" t="n">
         <v>2978</v>
@@ -1687,7 +1745,7 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>Universal · 12-mo postnatal</t>
+          <t>Universal · 6-mo postnatal</t>
         </is>
       </c>
       <c r="B11" s="10" t="inlineStr">
@@ -1696,16 +1754,16 @@
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>62901399</v>
+        <v>37331725</v>
       </c>
       <c r="D11" s="11" t="n">
         <v>11762050</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>51139349</v>
+        <v>25569674</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>9741852</v>
+        <v>5781749</v>
       </c>
       <c r="G11" s="11" t="n">
         <v>16365</v>
@@ -1714,7 +1772,7 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>Universal · 12-mo postnatal</t>
+          <t>Universal · 6-mo postnatal</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
@@ -1723,16 +1781,16 @@
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>3778862</v>
+        <v>2242739</v>
       </c>
       <c r="D12" s="11" t="n">
         <v>706616</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>3072245</v>
+        <v>1536123</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>2178659</v>
+        <v>1293025</v>
       </c>
       <c r="G12" s="11" t="n">
         <v>983</v>
@@ -1741,7 +1799,7 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>Universal · 12-mo postnatal</t>
+          <t>Universal · 6-mo postnatal</t>
         </is>
       </c>
       <c r="B13" s="10" t="inlineStr">
@@ -1750,18 +1808,126 @@
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>9734809</v>
+        <v>5777570</v>
       </c>
       <c r="D13" s="11" t="n">
         <v>1820330</v>
       </c>
       <c r="E13" s="11" t="n">
+        <v>3957240</v>
+      </c>
+      <c r="F13" s="11" t="n">
+        <v>2922020</v>
+      </c>
+      <c r="G13" s="11" t="n">
+        <v>2533</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>Universal · 12-mo postnatal</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="n">
+        <v>11446236</v>
+      </c>
+      <c r="D14" s="11" t="n">
+        <v>2140353</v>
+      </c>
+      <c r="E14" s="11" t="n">
+        <v>9305883</v>
+      </c>
+      <c r="F14" s="11" t="n">
+        <v>3876596</v>
+      </c>
+      <c r="G14" s="11" t="n">
+        <v>2978</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>Universal · 12-mo postnatal</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>Honolulu</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="n">
+        <v>62901399</v>
+      </c>
+      <c r="D15" s="11" t="n">
+        <v>11762050</v>
+      </c>
+      <c r="E15" s="11" t="n">
+        <v>51139349</v>
+      </c>
+      <c r="F15" s="11" t="n">
+        <v>9741852</v>
+      </c>
+      <c r="G15" s="11" t="n">
+        <v>16365</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>Universal · 12-mo postnatal</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>Kauai</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="n">
+        <v>3778862</v>
+      </c>
+      <c r="D16" s="11" t="n">
+        <v>706616</v>
+      </c>
+      <c r="E16" s="11" t="n">
+        <v>3072245</v>
+      </c>
+      <c r="F16" s="11" t="n">
+        <v>2178659</v>
+      </c>
+      <c r="G16" s="11" t="n">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>Universal · 12-mo postnatal</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>Maui</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="n">
+        <v>9734809</v>
+      </c>
+      <c r="D17" s="11" t="n">
+        <v>1820330</v>
+      </c>
+      <c r="E17" s="11" t="n">
         <v>7914479</v>
       </c>
-      <c r="F13" s="11" t="n">
+      <c r="F17" s="11" t="n">
         <v>4923404</v>
       </c>
-      <c r="G13" s="11" t="n">
+      <c r="G17" s="11" t="n">
         <v>2533</v>
       </c>
     </row>
